--- a/data/serie_modelo.xlsx
+++ b/data/serie_modelo.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30416"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\para cargar simulador electoral arg\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_F346819FBB6225D5DF1F731669765A205F2BC966" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{144563DA-BB05-4151-B950-4E7B96EF877F}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="244">
   <si>
     <t>YearMonth</t>
   </si>
@@ -743,16 +749,25 @@
   </si>
   <si>
     <t>S1</t>
+  </si>
+  <si>
+    <t>2026-08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -786,13 +801,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -830,7 +853,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -864,6 +887,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -898,9 +922,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1073,11 +1098,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I227"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I228"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="9" width="11.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1114,25 +1142,25 @@
         <v>235</v>
       </c>
       <c r="D2">
-        <v>334.2033333333333</v>
+        <v>334.20333333333332</v>
       </c>
       <c r="E2">
-        <v>227.754</v>
+        <v>227.75399999999999</v>
       </c>
       <c r="F2">
-        <v>1.67777392300069</v>
+        <v>1.6777739230006901</v>
       </c>
       <c r="G2">
         <v>3.16</v>
       </c>
       <c r="H2">
-        <v>142.5416356897516</v>
+        <v>142.54163568975159</v>
       </c>
       <c r="I2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1140,10 +1168,10 @@
         <v>235</v>
       </c>
       <c r="D3">
-        <v>397.03245</v>
+        <v>397.03244999999998</v>
       </c>
       <c r="E3">
-        <v>272.5307</v>
+        <v>272.53070000000002</v>
       </c>
       <c r="F3">
         <v>1.981124028835928</v>
@@ -1152,13 +1180,13 @@
         <v>3.14</v>
       </c>
       <c r="H3">
-        <v>143.8245104109594</v>
+        <v>143.82451041095939</v>
       </c>
       <c r="I3">
-        <v>98.48076175182847</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>98.480761751828467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1169,25 +1197,25 @@
         <v>241</v>
       </c>
       <c r="D4">
-        <v>394.2062</v>
+        <v>394.20620000000002</v>
       </c>
       <c r="E4">
-        <v>277.79945</v>
+        <v>277.79944999999998</v>
       </c>
       <c r="F4">
-        <v>2.043554231211219</v>
+        <v>2.0435542312112189</v>
       </c>
       <c r="G4">
         <v>3.14</v>
       </c>
       <c r="H4">
-        <v>145.118931004658</v>
+        <v>145.11893100465801</v>
       </c>
       <c r="I4">
-        <v>97.60234068565757</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>97.602340685657566</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1198,25 +1226,25 @@
         <v>241</v>
       </c>
       <c r="D5">
-        <v>443.1637142857143</v>
+        <v>443.16371428571432</v>
       </c>
       <c r="E5">
-        <v>306.1382380952381</v>
+        <v>306.13823809523808</v>
       </c>
       <c r="F5">
-        <v>2.368826739715107</v>
+        <v>2.3688267397151068</v>
       </c>
       <c r="G5">
         <v>3.14</v>
       </c>
       <c r="H5">
-        <v>146.4250013836999</v>
+        <v>146.42500138369991</v>
       </c>
       <c r="I5">
-        <v>96.73175489163287</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>96.731754891632875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1227,10 +1255,10 @@
         <v>241</v>
       </c>
       <c r="D6">
-        <v>476.65705</v>
+        <v>476.65705000000003</v>
       </c>
       <c r="E6">
-        <v>319.74165</v>
+        <v>319.74164999999999</v>
       </c>
       <c r="F6">
         <v>1.97699051445354</v>
@@ -1242,10 +1270,10 @@
         <v>147.1571263906184</v>
       </c>
       <c r="I6">
-        <v>96.86356290444589</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>96.863562904445885</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1256,10 +1284,10 @@
         <v>241</v>
       </c>
       <c r="D7">
-        <v>528.8496</v>
+        <v>528.84960000000001</v>
       </c>
       <c r="E7">
-        <v>344.0305</v>
+        <v>344.03050000000002</v>
       </c>
       <c r="F7">
         <v>1.861109390011157</v>
@@ -1268,13 +1296,13 @@
         <v>3.15</v>
       </c>
       <c r="H7">
-        <v>148.7758547809152</v>
+        <v>148.77585478091521</v>
       </c>
       <c r="I7">
-        <v>95.50646156487642</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>95.506461564876417</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1285,25 +1313,25 @@
         <v>241</v>
       </c>
       <c r="D8">
-        <v>555.5619545454546</v>
+        <v>555.56195454545457</v>
       </c>
       <c r="E8">
-        <v>321.5014090909091</v>
+        <v>321.50140909090908</v>
       </c>
       <c r="F8">
-        <v>1.739513094257967</v>
+        <v>1.7395130942579671</v>
       </c>
       <c r="G8">
         <v>3.17</v>
       </c>
       <c r="H8">
-        <v>149.9660616191626</v>
+        <v>149.96606161916259</v>
       </c>
       <c r="I8">
         <v>95.35005138594677</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1314,25 +1342,25 @@
         <v>241</v>
       </c>
       <c r="D9">
-        <v>552.7048095238094</v>
+        <v>552.70480952380944</v>
       </c>
       <c r="E9">
-        <v>297.9537142857143</v>
+        <v>297.95371428571428</v>
       </c>
       <c r="F9">
-        <v>1.334346165128807</v>
+        <v>1.3343461651288071</v>
       </c>
       <c r="G9">
         <v>3.15</v>
       </c>
       <c r="H9">
-        <v>150.8658579888775</v>
+        <v>150.86585798887751</v>
       </c>
       <c r="I9">
-        <v>94.1833735334781</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>94.183373533478104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1346,7 +1374,7 @@
         <v>561.7461428571429</v>
       </c>
       <c r="E10">
-        <v>293.2555714285714</v>
+        <v>293.25557142857139</v>
       </c>
       <c r="F10">
         <v>1.207620822336096</v>
@@ -1355,13 +1383,13 @@
         <v>3.04</v>
       </c>
       <c r="H10">
-        <v>151.7710531368108</v>
+        <v>151.77105313681079</v>
       </c>
       <c r="I10">
-        <v>90.35231643212897</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>90.352316432128973</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1375,7 +1403,7 @@
         <v>626.6585</v>
       </c>
       <c r="E11">
-        <v>335.1833636363636</v>
+        <v>335.18336363636359</v>
       </c>
       <c r="F11">
         <v>1.268698417376326</v>
@@ -1384,13 +1412,13 @@
         <v>3.02</v>
       </c>
       <c r="H11">
-        <v>152.378137349358</v>
+        <v>152.37813734935801</v>
       </c>
       <c r="I11">
-        <v>89.40029212919032</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>89.400292129190319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1401,25 +1429,25 @@
         <v>241</v>
       </c>
       <c r="D12">
-        <v>668.4343809523809</v>
+        <v>668.43438095238093</v>
       </c>
       <c r="E12">
-        <v>350.4878571428571</v>
+        <v>350.48785714285708</v>
       </c>
       <c r="F12">
-        <v>1.394679972739093</v>
+        <v>1.3946799727390931</v>
       </c>
       <c r="G12">
         <v>3.03</v>
       </c>
       <c r="H12">
-        <v>153.1400280361048</v>
+        <v>153.14002803610481</v>
       </c>
       <c r="I12">
-        <v>89.2500692403699</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>89.250069240369896</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1433,7 +1461,7 @@
         <v>798.7311428571428</v>
       </c>
       <c r="E13">
-        <v>417.6446666666667</v>
+        <v>417.64466666666669</v>
       </c>
       <c r="F13">
         <v>1.441835312194548</v>
@@ -1442,13 +1470,13 @@
         <v>3.08</v>
       </c>
       <c r="H13">
-        <v>153.9057281762853</v>
+        <v>153.90572817628529</v>
       </c>
       <c r="I13">
-        <v>90.27148523400795</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>90.271485234007955</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1459,10 +1487,10 @@
         <v>241</v>
       </c>
       <c r="D14">
-        <v>1487.969272727273</v>
+        <v>1487.9692727272729</v>
       </c>
       <c r="E14">
-        <v>707.0680909090909</v>
+        <v>707.06809090909087</v>
       </c>
       <c r="F14">
         <v>1.378743243122023</v>
@@ -1474,10 +1502,10 @@
         <v>154.5213510889904</v>
       </c>
       <c r="I14">
-        <v>94.29066115597534</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>94.290661155975343</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1488,25 +1516,25 @@
         <v>241</v>
       </c>
       <c r="D15">
-        <v>1789.966111111111</v>
+        <v>1789.9661111111111</v>
       </c>
       <c r="E15">
         <v>768.1445555555556</v>
       </c>
       <c r="F15">
-        <v>1.427869330861398</v>
+        <v>1.4278693308613979</v>
       </c>
       <c r="G15">
         <v>3.33</v>
       </c>
       <c r="H15">
-        <v>154.9849151422574</v>
+        <v>154.98491514225739</v>
       </c>
       <c r="I15">
-        <v>96.91911931369913</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>96.919119313699127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1523,19 +1551,19 @@
         <v>805.7409090909091</v>
       </c>
       <c r="F16">
-        <v>1.36777543041184</v>
+        <v>1.3677754304118399</v>
       </c>
       <c r="G16">
         <v>3.43</v>
       </c>
       <c r="H16">
-        <v>155.4498698876841</v>
+        <v>155.44986988768409</v>
       </c>
       <c r="I16">
-        <v>99.5310103461352</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>99.531010346135204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1546,10 +1574,10 @@
         <v>241</v>
       </c>
       <c r="D17">
-        <v>1573.534</v>
+        <v>1573.5340000000001</v>
       </c>
       <c r="E17">
-        <v>741.4649499999999</v>
+        <v>741.46494999999993</v>
       </c>
       <c r="F17">
         <v>1.504587201794412</v>
@@ -1558,13 +1586,13 @@
         <v>3.46</v>
       </c>
       <c r="H17">
-        <v>156.2271192371225</v>
+        <v>156.22711923712251</v>
       </c>
       <c r="I17">
-        <v>99.90203379534624</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>99.902033795346242</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1578,10 +1606,10 @@
         <v>1644.651157894737</v>
       </c>
       <c r="E18">
-        <v>731.0996842105263</v>
+        <v>731.09968421052633</v>
       </c>
       <c r="F18">
-        <v>1.375139420411818</v>
+        <v>1.3751394204118179</v>
       </c>
       <c r="G18">
         <v>3.51</v>
@@ -1593,7 +1621,7 @@
         <v>100.9419370557266</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1607,7 +1635,7 @@
         <v>1862.939318181818</v>
       </c>
       <c r="E19">
-        <v>728.1470909090908</v>
+        <v>728.14709090909082</v>
       </c>
       <c r="F19">
         <v>1.357811894361254</v>
@@ -1616,13 +1644,13 @@
         <v>3.65</v>
       </c>
       <c r="H19">
-        <v>157.7931398803555</v>
+        <v>157.79313988035551</v>
       </c>
       <c r="I19">
         <v>104.3420588303235</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1633,10 +1661,10 @@
         <v>241</v>
       </c>
       <c r="D20">
-        <v>1786.433571428572</v>
+        <v>1786.4335714285719</v>
       </c>
       <c r="E20">
-        <v>655.3766666666667</v>
+        <v>655.37666666666667</v>
       </c>
       <c r="F20">
         <v>1.353924062468419</v>
@@ -1648,10 +1676,10 @@
         <v>158.2665192999965</v>
       </c>
       <c r="I20">
-        <v>105.1700233775096</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>105.17002337750959</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1662,10 +1690,10 @@
         <v>241</v>
       </c>
       <c r="D21">
-        <v>1457.10705</v>
+        <v>1457.1070500000001</v>
       </c>
       <c r="E21">
-        <v>562.8774000000001</v>
+        <v>562.87740000000008</v>
       </c>
       <c r="F21">
         <v>1.321658526861361</v>
@@ -1674,13 +1702,13 @@
         <v>3.73</v>
       </c>
       <c r="H21">
-        <v>158.7413188578965</v>
+        <v>158.74131885789649</v>
       </c>
       <c r="I21">
         <v>105.9921015268857</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1691,10 +1719,10 @@
         <v>241</v>
       </c>
       <c r="D22">
-        <v>1138.605318181818</v>
+        <v>1138.6053181818179</v>
       </c>
       <c r="E22">
-        <v>500.9805</v>
+        <v>500.98050000000001</v>
       </c>
       <c r="F22">
         <v>1.340302011764134</v>
@@ -1703,13 +1731,13 @@
         <v>3.77</v>
       </c>
       <c r="H22">
-        <v>159.3762841333281</v>
+        <v>159.37628413332811</v>
       </c>
       <c r="I22">
-        <v>106.7019382941048</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>106.70193829410481</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1720,25 +1748,25 @@
         <v>241</v>
       </c>
       <c r="D23">
-        <v>1038.674727272727</v>
+        <v>1038.6747272727271</v>
       </c>
       <c r="E23">
-        <v>453.682909090909</v>
+        <v>453.68290909090899</v>
       </c>
       <c r="F23">
-        <v>1.234524606203235</v>
+        <v>1.2345246062032349</v>
       </c>
       <c r="G23">
         <v>3.81</v>
       </c>
       <c r="H23">
-        <v>160.332541838128</v>
+        <v>160.33254183812801</v>
       </c>
       <c r="I23">
         <v>107.1909088968944</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1749,25 +1777,25 @@
         <v>241</v>
       </c>
       <c r="D24">
-        <v>900.2059523809525</v>
+        <v>900.20595238095245</v>
       </c>
       <c r="E24">
-        <v>410.8858571428571</v>
+        <v>410.88585714285711</v>
       </c>
       <c r="F24">
-        <v>1.111036397751097</v>
+        <v>1.1110363977510971</v>
       </c>
       <c r="G24">
         <v>3.84</v>
       </c>
       <c r="H24">
-        <v>161.615202172833</v>
+        <v>161.61520217283299</v>
       </c>
       <c r="I24">
         <v>107.1775117079309</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1778,10 +1806,10 @@
         <v>241</v>
       </c>
       <c r="D25">
-        <v>820.5579523809524</v>
+        <v>820.55795238095243</v>
       </c>
       <c r="E25">
-        <v>389.2355238095238</v>
+        <v>389.23552380952378</v>
       </c>
       <c r="F25">
         <v>1.223654795728635</v>
@@ -1790,13 +1818,13 @@
         <v>3.84</v>
       </c>
       <c r="H25">
-        <v>162.7465085880428</v>
+        <v>162.74650858804279</v>
       </c>
       <c r="I25">
-        <v>106.4324843177069</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>106.43248431770689</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1807,10 +1835,10 @@
         <v>241</v>
       </c>
       <c r="D26">
-        <v>708.7776190476191</v>
+        <v>708.77761904761905</v>
       </c>
       <c r="E26">
-        <v>363.1823809523809</v>
+        <v>363.18238095238092</v>
       </c>
       <c r="F26">
         <v>1.14581891341424</v>
@@ -1819,13 +1847,13 @@
         <v>3.83</v>
       </c>
       <c r="H26">
-        <v>164.0484806567472</v>
+        <v>164.04848065674719</v>
       </c>
       <c r="I26">
-        <v>105.3128138787661</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>105.31281387876609</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1839,7 +1867,7 @@
         <v>725.7213684210526</v>
       </c>
       <c r="E27">
-        <v>368.4194736842105</v>
+        <v>368.41947368421052</v>
       </c>
       <c r="F27">
         <v>1.158551833085284</v>
@@ -1848,13 +1876,13 @@
         <v>3.81</v>
       </c>
       <c r="H27">
-        <v>165.3608685020012</v>
+        <v>165.36086850200121</v>
       </c>
       <c r="I27">
         <v>103.9314261050237</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1865,10 +1893,10 @@
         <v>241</v>
       </c>
       <c r="D28">
-        <v>719.9208636363636</v>
+        <v>719.92086363636361</v>
       </c>
       <c r="E28">
-        <v>358.5960909090909</v>
+        <v>358.59609090909089</v>
       </c>
       <c r="F28">
         <v>1.04431645461675</v>
@@ -1877,13 +1905,13 @@
         <v>3.81</v>
       </c>
       <c r="H28">
-        <v>166.8491163185192</v>
+        <v>166.84911631851921</v>
       </c>
       <c r="I28">
         <v>103.0043866253952</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1894,13 +1922,13 @@
         <v>241</v>
       </c>
       <c r="D29">
-        <v>711.6722105263158</v>
+        <v>711.67221052631578</v>
       </c>
       <c r="E29">
-        <v>343.0140526315789</v>
+        <v>343.01405263157892</v>
       </c>
       <c r="F29">
-        <v>1.259281824347695</v>
+        <v>1.2592818243476951</v>
       </c>
       <c r="G29">
         <v>3.8</v>
@@ -1909,10 +1937,10 @@
         <v>168.5176074817044</v>
       </c>
       <c r="I29">
-        <v>101.7168652520729</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>101.71686525207291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1926,22 +1954,22 @@
         <v>790.2707894736842</v>
       </c>
       <c r="E30">
-        <v>365.0964736842105</v>
+        <v>365.09647368421048</v>
       </c>
       <c r="F30">
-        <v>1.187212555157778</v>
+        <v>1.1872125551577779</v>
       </c>
       <c r="G30">
         <v>3.85</v>
       </c>
       <c r="H30">
-        <v>170.5398187714848</v>
+        <v>170.53981877148479</v>
       </c>
       <c r="I30">
         <v>101.8332461047641</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -1952,13 +1980,13 @@
         <v>241</v>
       </c>
       <c r="D31">
-        <v>704.2781739130435</v>
+        <v>704.27817391304347</v>
       </c>
       <c r="E31">
-        <v>321.5396086956522</v>
+        <v>321.53960869565219</v>
       </c>
       <c r="F31">
-        <v>1.337283512395525</v>
+        <v>1.3372835123955249</v>
       </c>
       <c r="G31">
         <v>3.86</v>
@@ -1970,7 +1998,7 @@
         <v>100.9868922281884</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -1981,7 +2009,7 @@
         <v>241</v>
       </c>
       <c r="D32">
-        <v>629.9210476190476</v>
+        <v>629.92104761904761</v>
       </c>
       <c r="E32">
         <v>300.3308571428571</v>
@@ -1993,13 +2021,13 @@
         <v>3.88</v>
       </c>
       <c r="H32">
-        <v>173.7950828321949</v>
+        <v>173.79508283219491</v>
       </c>
       <c r="I32">
         <v>100.7045043397306</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2010,25 +2038,25 @@
         <v>241</v>
       </c>
       <c r="D33">
-        <v>766.1202999999999</v>
+        <v>766.12029999999993</v>
       </c>
       <c r="E33">
-        <v>370.9449</v>
+        <v>370.94490000000002</v>
       </c>
       <c r="F33">
-        <v>1.591853902646767</v>
+        <v>1.5918539026467671</v>
       </c>
       <c r="G33">
         <v>3.9</v>
       </c>
       <c r="H33">
-        <v>175.0116484120203</v>
+        <v>175.01164841202029</v>
       </c>
       <c r="I33">
         <v>100.5199600029048</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -2039,25 +2067,25 @@
         <v>241</v>
       </c>
       <c r="D34">
-        <v>804.7517727272727</v>
+        <v>804.75177272727274</v>
       </c>
       <c r="E34">
-        <v>387.9392727272727</v>
+        <v>387.93927272727268</v>
       </c>
       <c r="F34">
-        <v>1.609848654587582</v>
+        <v>1.6098486545875821</v>
       </c>
       <c r="G34">
         <v>3.93</v>
       </c>
       <c r="H34">
-        <v>176.2367299509044</v>
+        <v>176.23672995090439</v>
       </c>
       <c r="I34">
-        <v>100.5890669954971</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>100.58906699549711</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2068,10 +2096,10 @@
         <v>241</v>
       </c>
       <c r="D35">
-        <v>765.3119047619048</v>
+        <v>765.31190476190477</v>
       </c>
       <c r="E35">
-        <v>374.7698571428572</v>
+        <v>374.76985714285718</v>
       </c>
       <c r="F35">
         <v>1.686758964614492</v>
@@ -2083,10 +2111,10 @@
         <v>177.6466237905116</v>
       </c>
       <c r="I35">
-        <v>99.79074106696144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>99.790741066961445</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2097,25 +2125,25 @@
         <v>241</v>
       </c>
       <c r="D36">
-        <v>713.5094545454546</v>
+        <v>713.50945454545456</v>
       </c>
       <c r="E36">
-        <v>347.4285454545454</v>
+        <v>347.42854545454537</v>
       </c>
       <c r="F36">
-        <v>1.796474483361829</v>
+        <v>1.7964744833618289</v>
       </c>
       <c r="G36">
         <v>3.94</v>
       </c>
       <c r="H36">
-        <v>178.8901501570452</v>
+        <v>178.89015015704521</v>
       </c>
       <c r="I36">
-        <v>99.34921700863121</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>99.349217008631214</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2126,10 +2154,10 @@
         <v>241</v>
       </c>
       <c r="D37">
-        <v>703.789</v>
+        <v>703.78899999999999</v>
       </c>
       <c r="E37">
-        <v>356.7000952380952</v>
+        <v>356.70009523809517</v>
       </c>
       <c r="F37">
         <v>1.771250029115307</v>
@@ -2138,13 +2166,13 @@
         <v>3.95</v>
       </c>
       <c r="H37">
-        <v>180.1423812081445</v>
+        <v>180.14238120814451</v>
       </c>
       <c r="I37">
-        <v>98.90900931653385</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>98.909009316533854</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -2155,10 +2183,10 @@
         <v>241</v>
       </c>
       <c r="D38">
-        <v>613.9955</v>
+        <v>613.99549999999999</v>
       </c>
       <c r="E38">
-        <v>330.30505</v>
+        <v>330.30504999999999</v>
       </c>
       <c r="F38">
         <v>1.703713568441924</v>
@@ -2170,10 +2198,10 @@
         <v>181.5835202578096</v>
       </c>
       <c r="I38">
-        <v>98.37243241246586</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>98.372432412465855</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2184,10 +2212,10 @@
         <v>241</v>
       </c>
       <c r="D39">
-        <v>546.1220999999999</v>
+        <v>546.12209999999993</v>
       </c>
       <c r="E39">
-        <v>320.0705</v>
+        <v>320.07049999999998</v>
       </c>
       <c r="F39">
         <v>2.42189766542272</v>
@@ -2196,13 +2224,13 @@
         <v>3.97</v>
       </c>
       <c r="H39">
-        <v>182.8546048996143</v>
+        <v>182.85460489961429</v>
       </c>
       <c r="I39">
         <v>97.93530054203643</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -2213,13 +2241,13 @@
         <v>241</v>
       </c>
       <c r="D40">
-        <v>521.2415454545454</v>
+        <v>521.24154545454542</v>
       </c>
       <c r="E40">
-        <v>314.8272272727273</v>
+        <v>314.82722727272733</v>
       </c>
       <c r="F40">
-        <v>2.336224878378703</v>
+        <v>2.3362248783787032</v>
       </c>
       <c r="G40">
         <v>3.98</v>
@@ -2228,10 +2256,10 @@
         <v>184.3174417388112</v>
       </c>
       <c r="I40">
-        <v>97.40276682192459</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>97.402766821924587</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -2242,10 +2270,10 @@
         <v>241</v>
       </c>
       <c r="D41">
-        <v>497.0952</v>
+        <v>497.09519999999998</v>
       </c>
       <c r="E41">
-        <v>303.2433</v>
+        <v>303.24329999999998</v>
       </c>
       <c r="F41">
         <v>2.163692332199135</v>
@@ -2260,7 +2288,7 @@
         <v>100.3711274781426</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -2271,25 +2299,25 @@
         <v>241</v>
       </c>
       <c r="D42">
-        <v>541.6190526315789</v>
+        <v>541.61905263157894</v>
       </c>
       <c r="E42">
-        <v>308.8466842105263</v>
+        <v>308.84668421052629</v>
       </c>
       <c r="F42">
         <v>2.178610935120338</v>
       </c>
       <c r="G42">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="H42">
-        <v>186.9069174777997</v>
+        <v>186.90691747779971</v>
       </c>
       <c r="I42">
         <v>100.1560935519864</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -2300,25 +2328,25 @@
         <v>241</v>
       </c>
       <c r="D43">
-        <v>566.2754347826086</v>
+        <v>566.27543478260861</v>
       </c>
       <c r="E43">
-        <v>317.1883913043479</v>
+        <v>317.18839130434787</v>
       </c>
       <c r="F43">
-        <v>2.423661865819389</v>
+        <v>2.4236618658193891</v>
       </c>
       <c r="G43">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="H43">
         <v>188.4021728176221</v>
       </c>
       <c r="I43">
-        <v>99.36120392062145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>99.361203920621449</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -2329,7 +2357,7 @@
         <v>241</v>
       </c>
       <c r="D44">
-        <v>533.00965</v>
+        <v>533.00964999999997</v>
       </c>
       <c r="E44">
         <v>316.47055</v>
@@ -2347,7 +2375,7 @@
         <v>102.1354888264181</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -2358,10 +2386,10 @@
         <v>241</v>
       </c>
       <c r="D45">
-        <v>580.7612857142857</v>
+        <v>580.76128571428569</v>
       </c>
       <c r="E45">
-        <v>324.3525714285714</v>
+        <v>324.35257142857142</v>
       </c>
       <c r="F45">
         <v>2.338864624471499</v>
@@ -2370,13 +2398,13 @@
         <v>4.29</v>
       </c>
       <c r="H45">
-        <v>191.2387559315642</v>
+        <v>191.23875593156421</v>
       </c>
       <c r="I45">
-        <v>101.1896369749737</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>101.18963697497369</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -2387,16 +2415,16 @@
         <v>241</v>
       </c>
       <c r="D46">
-        <v>604.6192727272727</v>
+        <v>604.61927272727269</v>
       </c>
       <c r="E46">
-        <v>332.1161363636364</v>
+        <v>332.11613636363637</v>
       </c>
       <c r="F46">
         <v>2.29441622776582</v>
       </c>
       <c r="G46">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="H46">
         <v>192.5774272230851</v>
@@ -2405,7 +2433,7 @@
         <v>100.0177660532769</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -2416,25 +2444,25 @@
         <v>241</v>
       </c>
       <c r="D47">
-        <v>595.0576</v>
+        <v>595.05759999999998</v>
       </c>
       <c r="E47">
         <v>318.8811</v>
       </c>
       <c r="F47">
-        <v>2.478405000663605</v>
+        <v>2.4784050006636051</v>
       </c>
       <c r="G47">
         <v>4.34</v>
       </c>
       <c r="H47">
-        <v>194.1180466408698</v>
+        <v>194.11804664086981</v>
       </c>
       <c r="I47">
-        <v>100.8505967880427</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>100.85059678804269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -2445,13 +2473,13 @@
         <v>241</v>
       </c>
       <c r="D48">
-        <v>718.992</v>
+        <v>718.99199999999996</v>
       </c>
       <c r="E48">
-        <v>367.8347826086957</v>
+        <v>367.83478260869572</v>
       </c>
       <c r="F48">
-        <v>2.246161588654069</v>
+        <v>2.2461615886540689</v>
       </c>
       <c r="G48">
         <v>4.43</v>
@@ -2463,7 +2491,7 @@
         <v>102.1249688599565</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -2474,10 +2502,10 @@
         <v>241</v>
       </c>
       <c r="D49">
-        <v>877.8204761904761</v>
+        <v>877.82047619047614</v>
       </c>
       <c r="E49">
-        <v>422.4115714285714</v>
+        <v>422.41157142857139</v>
       </c>
       <c r="F49">
         <v>2.640606704855418</v>
@@ -2486,13 +2514,13 @@
         <v>4.43</v>
       </c>
       <c r="H49">
-        <v>197.2363589421087</v>
+        <v>197.23635894210869</v>
       </c>
       <c r="I49">
         <v>101.3144532340839</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -2506,22 +2534,22 @@
         <v>904.8691500000001</v>
       </c>
       <c r="E50">
-        <v>420.78115</v>
+        <v>420.78115000000003</v>
       </c>
       <c r="F50">
-        <v>2.620903580441495</v>
+        <v>2.6209035804414951</v>
       </c>
       <c r="G50">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="H50">
-        <v>198.4197770957614</v>
+        <v>198.41977709576139</v>
       </c>
       <c r="I50">
-        <v>101.8468759651337</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>101.84687596513371</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -2532,25 +2560,25 @@
         <v>241</v>
       </c>
       <c r="D51">
-        <v>893.0409</v>
+        <v>893.04089999999997</v>
       </c>
       <c r="E51">
-        <v>402.8106</v>
+        <v>402.81060000000002</v>
       </c>
       <c r="F51">
-        <v>2.622001654259719</v>
+        <v>2.6220016542597189</v>
       </c>
       <c r="G51">
         <v>4.62</v>
       </c>
       <c r="H51">
-        <v>199.610295758336</v>
+        <v>199.61029575833601</v>
       </c>
       <c r="I51">
         <v>104.403171808195</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2561,25 +2589,25 @@
         <v>241</v>
       </c>
       <c r="D52">
-        <v>926.8064761904762</v>
+        <v>926.80647619047625</v>
       </c>
       <c r="E52">
-        <v>397.6105714285715</v>
+        <v>397.61057142857152</v>
       </c>
       <c r="F52">
-        <v>2.710471217080748</v>
+        <v>2.7104712170807481</v>
       </c>
       <c r="G52">
-        <v>4.73</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="H52">
-        <v>201.2071781244026</v>
+        <v>201.20717812440259</v>
       </c>
       <c r="I52">
-        <v>106.0406365209842</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>106.04063652098419</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -2590,25 +2618,25 @@
         <v>241</v>
       </c>
       <c r="D53">
-        <v>850.9102</v>
+        <v>850.91020000000003</v>
       </c>
       <c r="E53">
         <v>394.0702</v>
       </c>
       <c r="F53">
-        <v>2.748843964990564</v>
+        <v>2.7488439649905638</v>
       </c>
       <c r="G53">
         <v>4.78</v>
       </c>
       <c r="H53">
-        <v>203.0180427275222</v>
+        <v>203.01804272752219</v>
       </c>
       <c r="I53">
-        <v>106.2057219842358</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>106.20572198423579</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2619,25 +2647,25 @@
         <v>241</v>
       </c>
       <c r="D54">
-        <v>822.434</v>
+        <v>822.43399999999997</v>
       </c>
       <c r="E54">
-        <v>364.764</v>
+        <v>364.76400000000001</v>
       </c>
       <c r="F54">
-        <v>2.55771776647407</v>
+        <v>2.5577177664740698</v>
       </c>
       <c r="G54">
         <v>4.71</v>
       </c>
       <c r="H54">
-        <v>204.4391690266149</v>
+        <v>204.43916902661491</v>
       </c>
       <c r="I54">
         <v>103.922947431941</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2648,13 +2676,13 @@
         <v>241</v>
       </c>
       <c r="D55">
-        <v>823.1161818181819</v>
+        <v>823.11618181818187</v>
       </c>
       <c r="E55">
-        <v>331.6535909090909</v>
+        <v>331.65359090909089</v>
       </c>
       <c r="F55">
-        <v>2.255543500957491</v>
+        <v>2.2555435009574909</v>
       </c>
       <c r="G55">
         <v>4.92</v>
@@ -2666,7 +2694,7 @@
         <v>107.5881611915583</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -2677,13 +2705,13 @@
         <v>241</v>
       </c>
       <c r="D56">
-        <v>967.3051499999999</v>
+        <v>967.30514999999991</v>
       </c>
       <c r="E56">
-        <v>346.9337</v>
+        <v>346.93369999999999</v>
       </c>
       <c r="F56">
-        <v>1.903894039426763</v>
+        <v>1.9038940394267629</v>
       </c>
       <c r="G56">
         <v>5.07</v>
@@ -2692,10 +2720,10 @@
         <v>207.9293545202373</v>
       </c>
       <c r="I56">
-        <v>109.9883810090819</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>109.98838100908191</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -2706,25 +2734,25 @@
         <v>241</v>
       </c>
       <c r="D57">
-        <v>1089.325272727273</v>
+        <v>1089.3252727272729</v>
       </c>
       <c r="E57">
-        <v>376.1126818181818</v>
+        <v>376.11268181818178</v>
       </c>
       <c r="F57">
-        <v>2.141538140195517</v>
+        <v>2.1415381401955171</v>
       </c>
       <c r="G57">
         <v>5.9</v>
       </c>
       <c r="H57">
-        <v>209.5927893563991</v>
+        <v>209.59278935639909</v>
       </c>
       <c r="I57">
         <v>126.9785401117653</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -2735,25 +2763,25 @@
         <v>241</v>
       </c>
       <c r="D58">
-        <v>1128.660666666667</v>
+        <v>1128.6606666666671</v>
       </c>
       <c r="E58">
         <v>390.2235714285714</v>
       </c>
       <c r="F58">
-        <v>1.985347773591628</v>
+        <v>1.9853477735916281</v>
       </c>
       <c r="G58">
         <v>5.93</v>
       </c>
       <c r="H58">
-        <v>211.0599388818939</v>
+        <v>211.05993888189391</v>
       </c>
       <c r="I58">
         <v>126.7370344643038</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -2767,22 +2795,22 @@
         <v>1091.756095238095</v>
       </c>
       <c r="E59">
-        <v>365.8994761904762</v>
+        <v>365.89947619047621</v>
       </c>
       <c r="F59">
-        <v>1.843371161710254</v>
+        <v>1.8433711617102539</v>
       </c>
       <c r="G59">
         <v>6.29</v>
       </c>
       <c r="H59">
-        <v>212.7484183929491</v>
+        <v>212.74841839294911</v>
       </c>
       <c r="I59">
-        <v>133.3641068384578</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>133.36410683845779</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -2796,22 +2824,22 @@
         <v>1038.97347826087</v>
       </c>
       <c r="E60">
-        <v>329.8957391304348</v>
+        <v>329.89573913043478</v>
       </c>
       <c r="F60">
-        <v>1.80381622992238</v>
+        <v>1.8038162299223801</v>
       </c>
       <c r="G60">
         <v>6.35</v>
       </c>
       <c r="H60">
-        <v>214.6631541584856</v>
+        <v>214.66315415848561</v>
       </c>
       <c r="I60">
-        <v>133.4353423992032</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>133.43534239920319</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -2822,10 +2850,10 @@
         <v>241</v>
       </c>
       <c r="D61">
-        <v>917.6812105263158</v>
+        <v>917.68121052631579</v>
       </c>
       <c r="E61">
-        <v>313.2573684210527</v>
+        <v>313.25736842105272</v>
       </c>
       <c r="F61">
         <v>1.68784684625814</v>
@@ -2834,13 +2862,13 @@
         <v>6.28</v>
       </c>
       <c r="H61">
-        <v>216.5951225459119</v>
+        <v>216.59512254591189</v>
       </c>
       <c r="I61">
-        <v>130.7873157748759</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>130.78731577487591</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -2851,10 +2879,10 @@
         <v>241</v>
       </c>
       <c r="D62">
-        <v>888.6396190476191</v>
+        <v>888.63961904761914</v>
       </c>
       <c r="E62">
-        <v>301.2416190476191</v>
+        <v>301.24161904761911</v>
       </c>
       <c r="F62">
         <v>1.669391823583031</v>
@@ -2863,13 +2891,13 @@
         <v>6.32</v>
       </c>
       <c r="H62">
-        <v>218.3278835262792</v>
+        <v>218.32788352627921</v>
       </c>
       <c r="I62">
-        <v>130.5757500027196</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>130.57575000271959</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -2880,25 +2908,25 @@
         <v>241</v>
       </c>
       <c r="D63">
-        <v>1197.1326</v>
+        <v>1197.1325999999999</v>
       </c>
       <c r="E63">
-        <v>323.42215</v>
+        <v>323.42214999999999</v>
       </c>
       <c r="F63">
-        <v>1.686828266814354</v>
+        <v>1.6868282668143539</v>
       </c>
       <c r="G63">
         <v>6.42</v>
       </c>
       <c r="H63">
-        <v>220.2928344780157</v>
+        <v>220.29283447801569</v>
       </c>
       <c r="I63">
         <v>131.4586937526596</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -2909,7 +2937,7 @@
         <v>241</v>
       </c>
       <c r="D64">
-        <v>1036.4516</v>
+        <v>1036.4516000000001</v>
       </c>
       <c r="E64">
         <v>299.51835</v>
@@ -2921,13 +2949,13 @@
         <v>6.78</v>
       </c>
       <c r="H64">
-        <v>222.4957628227959</v>
+        <v>222.49576282279591</v>
       </c>
       <c r="I64">
         <v>137.4556527625663</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -2941,7 +2969,7 @@
         <v>1057.799238095238</v>
       </c>
       <c r="E65">
-        <v>287.9902857142857</v>
+        <v>287.99028571428568</v>
       </c>
       <c r="F65">
         <v>1.762382782079787</v>
@@ -2953,10 +2981,10 @@
         <v>224.9432162138466</v>
       </c>
       <c r="I65">
-        <v>158.2190448279323</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>158.21904482793229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -2967,25 +2995,25 @@
         <v>241</v>
       </c>
       <c r="D66">
-        <v>1114.378842105263</v>
+        <v>1114.3788421052629</v>
       </c>
       <c r="E66">
-        <v>302.172</v>
+        <v>302.17200000000003</v>
       </c>
       <c r="F66">
-        <v>1.83140943811004</v>
+        <v>1.8314094381100401</v>
       </c>
       <c r="G66">
         <v>7.82</v>
       </c>
       <c r="H66">
-        <v>226.0679322949159</v>
+        <v>226.06793229491589</v>
       </c>
       <c r="I66">
-        <v>156.0351513099181</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>156.03515130991809</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -2999,22 +3027,22 @@
         <v>1206.7547</v>
       </c>
       <c r="E67">
-        <v>316.86215</v>
+        <v>316.86214999999999</v>
       </c>
       <c r="F67">
         <v>1.913987955367201</v>
       </c>
       <c r="G67">
-        <v>8.380000000000001</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="H67">
-        <v>227.6504078209802</v>
+        <v>227.65040782098021</v>
       </c>
       <c r="I67">
         <v>166.0466971578889</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -3025,25 +3053,25 @@
         <v>241</v>
       </c>
       <c r="D68">
-        <v>1223.059818181818</v>
+        <v>1223.0598181818179</v>
       </c>
       <c r="E68">
-        <v>316.3416363636363</v>
+        <v>316.34163636363633</v>
       </c>
       <c r="F68">
-        <v>1.758606905264822</v>
+        <v>1.7586069052648221</v>
       </c>
       <c r="G68">
-        <v>9.369999999999999</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="H68">
         <v>229.2439606757271</v>
       </c>
       <c r="I68">
-        <v>184.3725843166355</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>184.37258431663551</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -3054,10 +3082,10 @@
         <v>241</v>
       </c>
       <c r="D69">
-        <v>1174.206363636364</v>
+        <v>1174.2063636363639</v>
       </c>
       <c r="E69">
-        <v>313.9394545454545</v>
+        <v>313.93945454545451</v>
       </c>
       <c r="F69">
         <v>1.420147142501418</v>
@@ -3066,13 +3094,13 @@
         <v>8.75</v>
       </c>
       <c r="H69">
-        <v>230.8486684004571</v>
+        <v>230.84866840045709</v>
       </c>
       <c r="I69">
         <v>170.9760717422611</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -3083,25 +3111,25 @@
         <v>241</v>
       </c>
       <c r="D70">
-        <v>1203.81875</v>
+        <v>1203.8187499999999</v>
       </c>
       <c r="E70">
-        <v>370.8108</v>
+        <v>370.81079999999997</v>
       </c>
       <c r="F70">
-        <v>1.74412651261189</v>
+        <v>1.7441265126118899</v>
       </c>
       <c r="G70">
         <v>8</v>
       </c>
       <c r="H70">
-        <v>232.6954577476608</v>
+        <v>232.69545774766081</v>
       </c>
       <c r="I70">
-        <v>155.0803371811892</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+        <v>155.08033718118921</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -3112,10 +3140,10 @@
         <v>241</v>
       </c>
       <c r="D71">
-        <v>1138.043181818182</v>
+        <v>1138.0431818181819</v>
       </c>
       <c r="E71">
-        <v>360.9323181818182</v>
+        <v>360.93231818181818</v>
       </c>
       <c r="F71">
         <v>1.679015908158062</v>
@@ -3127,10 +3155,10 @@
         <v>234.7897168673897</v>
       </c>
       <c r="I71">
-        <v>162.9188874252335</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>162.91888742523349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -3141,25 +3169,25 @@
         <v>241</v>
       </c>
       <c r="D72">
-        <v>1067.538909090909</v>
+        <v>1067.5389090909091</v>
       </c>
       <c r="E72">
-        <v>365.3403636363636</v>
+        <v>365.34036363636358</v>
       </c>
       <c r="F72">
-        <v>1.868805977388655</v>
+        <v>1.8688059773886549</v>
       </c>
       <c r="G72">
-        <v>9.199999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H72">
-        <v>236.6680346023288</v>
+        <v>236.66803460232879</v>
       </c>
       <c r="I72">
-        <v>175.3488324900966</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+        <v>175.34883249009661</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -3170,10 +3198,10 @@
         <v>241</v>
       </c>
       <c r="D73">
-        <v>1063.5464</v>
+        <v>1063.5463999999999</v>
       </c>
       <c r="E73">
-        <v>362.78345</v>
+        <v>362.78345000000002</v>
       </c>
       <c r="F73">
         <v>1.771609278972289</v>
@@ -3182,13 +3210,13 @@
         <v>9.43</v>
       </c>
       <c r="H73">
-        <v>238.5613788791474</v>
+        <v>238.56137887914741</v>
       </c>
       <c r="I73">
-        <v>178.3061044666161</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+        <v>178.30610446661609</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -3199,25 +3227,25 @@
         <v>241</v>
       </c>
       <c r="D74">
-        <v>927.5556363636365</v>
+        <v>927.55563636363649</v>
       </c>
       <c r="E74">
-        <v>355.8821363636364</v>
+        <v>355.88213636363639</v>
       </c>
       <c r="F74">
-        <v>1.976498817726514</v>
+        <v>1.9764988177265139</v>
       </c>
       <c r="G74">
-        <v>9.869999999999999</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="H74">
         <v>240.7084312890598</v>
       </c>
       <c r="I74">
-        <v>184.9611451428659</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>184.96114514286589</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -3228,25 +3256,25 @@
         <v>241</v>
       </c>
       <c r="D75">
-        <v>820.5583684210527</v>
+        <v>820.55836842105271</v>
       </c>
       <c r="E75">
-        <v>366.3271052631579</v>
+        <v>366.32710526315788</v>
       </c>
       <c r="F75">
         <v>1.847188757950742</v>
       </c>
       <c r="G75">
-        <v>9.529999999999999</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="H75">
         <v>242.8748071706612</v>
       </c>
       <c r="I75">
-        <v>176.9966665975333</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>176.99666659753331</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -3257,25 +3285,25 @@
         <v>241</v>
       </c>
       <c r="D76">
-        <v>803.6331904761904</v>
+        <v>803.63319047619041</v>
       </c>
       <c r="E76">
-        <v>360.2474761904762</v>
+        <v>360.24747619047622</v>
       </c>
       <c r="F76">
-        <v>1.680916789273386</v>
+        <v>1.6809167892733861</v>
       </c>
       <c r="G76">
-        <v>9.949999999999999</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="H76">
-        <v>246.2750544710505</v>
+        <v>246.27505447105051</v>
       </c>
       <c r="I76">
-        <v>182.2457093498427</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>182.24570934984271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -3286,10 +3314,10 @@
         <v>241</v>
       </c>
       <c r="D77">
-        <v>931.6199047619048</v>
+        <v>931.61990476190476</v>
       </c>
       <c r="E77">
-        <v>373.3832380952381</v>
+        <v>373.38323809523808</v>
       </c>
       <c r="F77">
         <v>1.462483957259084</v>
@@ -3298,13 +3326,13 @@
         <v>11.15</v>
       </c>
       <c r="H77">
-        <v>255.1409564320084</v>
+        <v>255.14095643200841</v>
       </c>
       <c r="I77">
-        <v>197.1284665849271</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>197.12846658492711</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -3318,22 +3346,22 @@
         <v>970.8811578947367</v>
       </c>
       <c r="E78">
-        <v>389.4742631578948</v>
+        <v>389.47426315789482</v>
       </c>
       <c r="F78">
-        <v>1.384981818657614</v>
+        <v>1.3849818186576139</v>
       </c>
       <c r="G78">
         <v>11.2</v>
       </c>
       <c r="H78">
-        <v>263.8157489506966</v>
+        <v>263.81574895069662</v>
       </c>
       <c r="I78">
-        <v>191.5014030367664</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+        <v>191.50140303676639</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -3344,25 +3372,25 @@
         <v>241</v>
       </c>
       <c r="D79">
-        <v>879.9109523809524</v>
+        <v>879.91095238095238</v>
       </c>
       <c r="E79">
-        <v>354.1244285714286</v>
+        <v>354.12442857142861</v>
       </c>
       <c r="F79">
-        <v>1.526287691467849</v>
+        <v>1.5262876914678489</v>
       </c>
       <c r="G79">
         <v>10.7</v>
       </c>
       <c r="H79">
-        <v>270.6749584234148</v>
+        <v>270.67495842341481</v>
       </c>
       <c r="I79">
         <v>178.3160168209935</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>87</v>
       </c>
@@ -3373,10 +3401,10 @@
         <v>241</v>
       </c>
       <c r="D80">
-        <v>787.5548095238096</v>
+        <v>787.55480952380958</v>
       </c>
       <c r="E80">
-        <v>325.1515238095238</v>
+        <v>325.15152380952378</v>
       </c>
       <c r="F80">
         <v>1.401645590676162</v>
@@ -3385,13 +3413,13 @@
         <v>10.45</v>
       </c>
       <c r="H80">
-        <v>275.5471076750363</v>
+        <v>275.54710767503627</v>
       </c>
       <c r="I80">
-        <v>171.0704859977766</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+        <v>171.07048599777659</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -3402,25 +3430,25 @@
         <v>241</v>
       </c>
       <c r="D81">
-        <v>797.9755238095238</v>
+        <v>797.97552380952379</v>
       </c>
       <c r="E81">
-        <v>319.4534761904762</v>
+        <v>319.45347619047618</v>
       </c>
       <c r="F81">
-        <v>1.512071039679526</v>
+        <v>1.5120710396795261</v>
       </c>
       <c r="G81">
         <v>11.3</v>
       </c>
       <c r="H81">
-        <v>279.4047671824868</v>
+        <v>279.40476718248681</v>
       </c>
       <c r="I81">
-        <v>182.431272404035</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+        <v>182.43127240403501</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -3431,25 +3459,25 @@
         <v>241</v>
       </c>
       <c r="D82">
-        <v>763.0040952380953</v>
+        <v>763.00409523809526</v>
       </c>
       <c r="E82">
-        <v>303.6757619047619</v>
+        <v>303.67576190476188</v>
       </c>
       <c r="F82">
-        <v>1.699718002359451</v>
+        <v>1.6997180023594509</v>
       </c>
       <c r="G82">
         <v>12.05</v>
       </c>
       <c r="H82">
-        <v>283.037029155859</v>
+        <v>283.03702915585899</v>
       </c>
       <c r="I82">
         <v>192.0429839055659</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -3463,7 +3491,7 @@
         <v>651.2329545454545</v>
       </c>
       <c r="E83">
-        <v>297.1178636363636</v>
+        <v>297.11786363636361</v>
       </c>
       <c r="F83">
         <v>1.872186275579709</v>
@@ -3472,13 +3500,13 @@
         <v>12.6</v>
       </c>
       <c r="H83">
-        <v>286.9995475640411</v>
+        <v>286.99954756404111</v>
       </c>
       <c r="I83">
         <v>198.035928307441</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>91</v>
       </c>
@@ -3489,25 +3517,25 @@
         <v>241</v>
       </c>
       <c r="D84">
-        <v>760.7651428571428</v>
+        <v>760.76514285714279</v>
       </c>
       <c r="E84">
-        <v>320.6892857142857</v>
+        <v>320.68928571428569</v>
       </c>
       <c r="F84">
-        <v>1.820887330956351</v>
+        <v>1.8208873309563509</v>
       </c>
       <c r="G84">
         <v>13.95</v>
       </c>
       <c r="H84">
-        <v>290.7305416823737</v>
+        <v>290.73054168237371</v>
       </c>
       <c r="I84">
-        <v>216.4403390752599</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
+        <v>216.44033907525991</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -3518,10 +3546,10 @@
         <v>241</v>
       </c>
       <c r="D85">
-        <v>718.740619047619</v>
+        <v>718.74061904761902</v>
       </c>
       <c r="E85">
-        <v>322.7975714285714</v>
+        <v>322.79757142857142</v>
       </c>
       <c r="F85">
         <v>1.705600851874292</v>
@@ -3530,13 +3558,13 @@
         <v>15.6</v>
       </c>
       <c r="H85">
-        <v>294.8007692659269</v>
+        <v>294.80076926592687</v>
       </c>
       <c r="I85">
         <v>238.6990229669257</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>93</v>
       </c>
@@ -3547,25 +3575,25 @@
         <v>241</v>
       </c>
       <c r="D86">
-        <v>759.3329090909091</v>
+        <v>759.33290909090908</v>
       </c>
       <c r="E86">
-        <v>360.8603636363636</v>
+        <v>360.86036363636362</v>
       </c>
       <c r="F86">
-        <v>1.646678167014407</v>
+        <v>1.6466781670144071</v>
       </c>
       <c r="G86">
         <v>14.18</v>
       </c>
       <c r="H86">
-        <v>298.338378497118</v>
+        <v>298.33837849711801</v>
       </c>
       <c r="I86">
-        <v>214.3985092778331</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>214.39850927783311</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -3576,10 +3604,10 @@
         <v>241</v>
       </c>
       <c r="D87">
-        <v>674.1912777777777</v>
+        <v>674.19127777777771</v>
       </c>
       <c r="E87">
-        <v>359.9043333333333</v>
+        <v>359.90433333333328</v>
       </c>
       <c r="F87">
         <v>1.602982404151861</v>
@@ -3588,13 +3616,13 @@
         <v>13</v>
       </c>
       <c r="H87">
-        <v>301.6201006605862</v>
+        <v>301.62010066058622</v>
       </c>
       <c r="I87">
-        <v>194.4185622895561</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+        <v>194.41856228955609</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>95</v>
       </c>
@@ -3605,10 +3633,10 @@
         <v>241</v>
       </c>
       <c r="D88">
-        <v>745.3308636363636</v>
+        <v>745.33086363636357</v>
       </c>
       <c r="E88">
-        <v>403.4742727272727</v>
+        <v>403.47427272727271</v>
       </c>
       <c r="F88">
         <v>1.635693694594414</v>
@@ -3617,13 +3645,13 @@
         <v>13.7</v>
       </c>
       <c r="H88">
-        <v>304.6363016671921</v>
+        <v>304.63630166719207</v>
       </c>
       <c r="I88">
         <v>202.8586674308392</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>96</v>
       </c>
@@ -3634,25 +3662,25 @@
         <v>241</v>
       </c>
       <c r="D89">
-        <v>732.2126000000001</v>
+        <v>732.21260000000007</v>
       </c>
       <c r="E89">
-        <v>436.98585</v>
+        <v>436.98585000000003</v>
       </c>
       <c r="F89">
-        <v>1.826382784347368</v>
+        <v>1.8263827843473679</v>
       </c>
       <c r="G89">
         <v>13.5</v>
       </c>
       <c r="H89">
-        <v>307.9873009855312</v>
+        <v>307.98730098553119</v>
       </c>
       <c r="I89">
-        <v>197.7222819291682</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
+        <v>197.72228192916819</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -3663,25 +3691,25 @@
         <v>241</v>
       </c>
       <c r="D90">
-        <v>684.1308421052631</v>
+        <v>684.13084210526313</v>
       </c>
       <c r="E90">
-        <v>414.0817894736842</v>
+        <v>414.08178947368418</v>
       </c>
       <c r="F90">
-        <v>1.653233918216754</v>
+        <v>1.6532339182167539</v>
       </c>
       <c r="G90">
         <v>12.93</v>
       </c>
       <c r="H90">
-        <v>310.759186694401</v>
+        <v>310.75918669440102</v>
       </c>
       <c r="I90">
         <v>187.6848442054212</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>98</v>
       </c>
@@ -3695,22 +3723,22 @@
         <v>593.1705454545455</v>
       </c>
       <c r="E91">
-        <v>410.211</v>
+        <v>410.21100000000001</v>
       </c>
       <c r="F91">
-        <v>1.863546047754363</v>
+        <v>1.8635460477543631</v>
       </c>
       <c r="G91">
         <v>12.52</v>
       </c>
       <c r="H91">
-        <v>314.7990561214282</v>
+        <v>314.79905612142818</v>
       </c>
       <c r="I91">
-        <v>179.4012905279986</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+        <v>179.40129052799861</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>99</v>
       </c>
@@ -3721,10 +3749,10 @@
         <v>241</v>
       </c>
       <c r="D92">
-        <v>603.4490952380953</v>
+        <v>603.44909523809531</v>
       </c>
       <c r="E92">
-        <v>391.0108095238095</v>
+        <v>391.01080952380948</v>
       </c>
       <c r="F92">
         <v>1.896234972352087</v>
@@ -3733,13 +3761,13 @@
         <v>12.6</v>
       </c>
       <c r="H92">
-        <v>318.2618457387638</v>
+        <v>318.26184573876378</v>
       </c>
       <c r="I92">
-        <v>178.5832093499289</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
+        <v>178.58320934992889</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>100</v>
       </c>
@@ -3750,25 +3778,25 @@
         <v>241</v>
       </c>
       <c r="D93">
-        <v>596.2184500000001</v>
+        <v>596.21845000000008</v>
       </c>
       <c r="E93">
-        <v>376.3952</v>
+        <v>376.39519999999999</v>
       </c>
       <c r="F93">
-        <v>2.090634470980541</v>
+        <v>2.0906344709805409</v>
       </c>
       <c r="G93">
         <v>12.55</v>
       </c>
       <c r="H93">
-        <v>321.4444641961514</v>
+        <v>321.44446419615139</v>
       </c>
       <c r="I93">
-        <v>176.1134117037253</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
+        <v>176.11341170372529</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>101</v>
       </c>
@@ -3779,25 +3807,25 @@
         <v>241</v>
       </c>
       <c r="D94">
-        <v>593.4207272727273</v>
+        <v>593.42072727272728</v>
       </c>
       <c r="E94">
         <v>398.0392727272727</v>
       </c>
       <c r="F94">
-        <v>1.937275235057132</v>
+        <v>1.9372752350571321</v>
       </c>
       <c r="G94">
         <v>13.3</v>
       </c>
       <c r="H94">
-        <v>324.6589088381129</v>
+        <v>324.65890883811289</v>
       </c>
       <c r="I94">
-        <v>184.7902154281525</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9">
+        <v>184.79021542815249</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>102</v>
       </c>
@@ -3808,13 +3836,13 @@
         <v>241</v>
       </c>
       <c r="D95">
-        <v>603.2001363636364</v>
+        <v>603.20013636363637</v>
       </c>
       <c r="E95">
         <v>415.2400909090909</v>
       </c>
       <c r="F95">
-        <v>2.036647126648294</v>
+        <v>2.0366471266482939</v>
       </c>
       <c r="G95">
         <v>14.79</v>
@@ -3823,10 +3851,10 @@
         <v>328.8794746530084</v>
       </c>
       <c r="I95">
-        <v>202.855160075587</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
+        <v>202.85516007558701</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>103</v>
       </c>
@@ -3837,25 +3865,25 @@
         <v>241</v>
       </c>
       <c r="D96">
-        <v>589.991380952381</v>
+        <v>589.99138095238095</v>
       </c>
       <c r="E96">
-        <v>451.9815714285714</v>
+        <v>451.98157142857139</v>
       </c>
       <c r="F96">
-        <v>1.917254972504365</v>
+        <v>1.9172549725043651</v>
       </c>
       <c r="G96">
         <v>15.32</v>
       </c>
       <c r="H96">
-        <v>332.8260283488445</v>
+        <v>332.82602834884449</v>
       </c>
       <c r="I96">
         <v>207.6328849183692</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -3866,10 +3894,10 @@
         <v>241</v>
       </c>
       <c r="D97">
-        <v>561.414</v>
+        <v>561.41399999999999</v>
       </c>
       <c r="E97">
-        <v>470.6068095238095</v>
+        <v>470.60680952380949</v>
       </c>
       <c r="F97">
         <v>1.777935535542563</v>
@@ -3878,13 +3906,13 @@
         <v>15.84</v>
       </c>
       <c r="H97">
-        <v>336.8199406890305</v>
+        <v>336.81994068903049</v>
       </c>
       <c r="I97">
         <v>212.1348580162701</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>105</v>
       </c>
@@ -3898,7 +3926,7 @@
         <v>555.1966666666666</v>
       </c>
       <c r="E98">
-        <v>477.7492857142857</v>
+        <v>477.74928571428569</v>
       </c>
       <c r="F98">
         <v>1.908506718702373</v>
@@ -3907,13 +3935,13 @@
         <v>15.6</v>
       </c>
       <c r="H98">
-        <v>340.5249600366099</v>
+        <v>340.52496003660991</v>
       </c>
       <c r="I98">
-        <v>206.6475702283601</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
+        <v>206.64757022836011</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>106</v>
       </c>
@@ -3924,10 +3952,10 @@
         <v>241</v>
       </c>
       <c r="D99">
-        <v>486.1205263157894</v>
+        <v>486.12052631578939</v>
       </c>
       <c r="E99">
-        <v>462.6902105263158</v>
+        <v>462.69021052631581</v>
       </c>
       <c r="F99">
         <v>1.748936835665043</v>
@@ -3936,13 +3964,13 @@
         <v>14.59</v>
       </c>
       <c r="H99">
-        <v>347.3354592373421</v>
+        <v>347.33545923734209</v>
       </c>
       <c r="I99">
-        <v>189.4788869803779</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
+        <v>189.47888698037789</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -3953,13 +3981,13 @@
         <v>242</v>
       </c>
       <c r="D100">
-        <v>478.0792272727273</v>
+        <v>478.07922727272728</v>
       </c>
       <c r="E100">
-        <v>494.1254545454545</v>
+        <v>494.12545454545449</v>
       </c>
       <c r="F100">
-        <v>1.797491396700072</v>
+        <v>1.7974913967000721</v>
       </c>
       <c r="G100">
         <v>14.17</v>
@@ -3971,7 +3999,7 @@
         <v>177.1168320696375</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>108</v>
       </c>
@@ -3982,13 +4010,13 @@
         <v>242</v>
       </c>
       <c r="D101">
-        <v>485.8800526315789</v>
+        <v>485.88005263157891</v>
       </c>
       <c r="E101">
         <v>546.0472631578948</v>
       </c>
       <c r="F101">
-        <v>3.137844491730198</v>
+        <v>3.1378444917301982</v>
       </c>
       <c r="G101">
         <v>13.87</v>
@@ -4000,7 +4028,7 @@
         <v>166.5389096992179</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>109</v>
       </c>
@@ -4011,25 +4039,25 @@
         <v>242</v>
       </c>
       <c r="D102">
-        <v>470.88005</v>
+        <v>470.88004999999998</v>
       </c>
       <c r="E102">
-        <v>566.6159</v>
+        <v>566.61590000000001</v>
       </c>
       <c r="F102">
-        <v>2.861860404084705</v>
+        <v>2.8618604040847049</v>
       </c>
       <c r="G102">
         <v>15.21</v>
       </c>
       <c r="H102">
-        <v>385.8209828807924</v>
+        <v>385.82098288079243</v>
       </c>
       <c r="I102">
-        <v>177.8271329142079</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
+        <v>177.82713291420791</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>110</v>
       </c>
@@ -4040,25 +4068,25 @@
         <v>242</v>
       </c>
       <c r="D103">
-        <v>450.0207727272727</v>
+        <v>450.02077272727269</v>
       </c>
       <c r="E103">
-        <v>486.1443181818182</v>
+        <v>486.14431818181822</v>
       </c>
       <c r="F103">
-        <v>3.032704679382211</v>
+        <v>3.0327046793822112</v>
       </c>
       <c r="G103">
         <v>14.86</v>
       </c>
       <c r="H103">
-        <v>397.3956123672162</v>
+        <v>397.39561236721619</v>
       </c>
       <c r="I103">
-        <v>168.6748750569776</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
+        <v>168.67487505697761</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>111</v>
       </c>
@@ -4069,25 +4097,25 @@
         <v>242</v>
       </c>
       <c r="D104">
-        <v>434.2017142857143</v>
+        <v>434.20171428571427</v>
       </c>
       <c r="E104">
-        <v>463.9322857142857</v>
+        <v>463.93228571428568</v>
       </c>
       <c r="F104">
-        <v>2.720017744232126</v>
+        <v>2.7200177442321261</v>
       </c>
       <c r="G104">
         <v>14.26</v>
       </c>
       <c r="H104">
-        <v>410.9070631877016</v>
+        <v>410.90706318770162</v>
       </c>
       <c r="I104">
         <v>156.5418905472678</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>112</v>
       </c>
@@ -4098,25 +4126,25 @@
         <v>242</v>
       </c>
       <c r="D105">
-        <v>545.8822380952381</v>
+        <v>545.88223809523811</v>
       </c>
       <c r="E105">
-        <v>464.8453333333334</v>
+        <v>464.84533333333337</v>
       </c>
       <c r="F105">
-        <v>2.622395458140858</v>
+        <v>2.6223954581408582</v>
       </c>
       <c r="G105">
         <v>14.11</v>
       </c>
       <c r="H105">
-        <v>428.1651598415851</v>
+        <v>428.16515984158508</v>
       </c>
       <c r="I105">
-        <v>148.6518586560765</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
+        <v>148.65185865607651</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>113</v>
       </c>
@@ -4127,25 +4155,25 @@
         <v>242</v>
       </c>
       <c r="D106">
-        <v>500.0991818181819</v>
+        <v>500.09918181818188</v>
       </c>
       <c r="E106">
-        <v>458.9662272727273</v>
+        <v>458.96622727272728</v>
       </c>
       <c r="F106">
-        <v>2.613319629260933</v>
+        <v>2.6133196292609329</v>
       </c>
       <c r="G106">
         <v>14.65</v>
       </c>
       <c r="H106">
-        <v>441.4382797966742</v>
+        <v>441.43827979667418</v>
       </c>
       <c r="I106">
-        <v>149.7001685737544</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
+        <v>149.70016857375441</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -4156,25 +4184,25 @@
         <v>242</v>
       </c>
       <c r="D107">
-        <v>488.4464</v>
+        <v>488.44639999999998</v>
       </c>
       <c r="E107">
-        <v>417.9612</v>
+        <v>417.96120000000002</v>
       </c>
       <c r="F107">
-        <v>2.707066913409314</v>
+        <v>2.7070669134093142</v>
       </c>
       <c r="G107">
         <v>15.07</v>
       </c>
       <c r="H107">
-        <v>450.2670453926077</v>
+        <v>450.26704539260771</v>
       </c>
       <c r="I107">
-        <v>150.9724647263922</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
+        <v>150.97246472639219</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>115</v>
       </c>
@@ -4185,13 +4213,13 @@
         <v>242</v>
       </c>
       <c r="D108">
-        <v>461.4487391304348</v>
+        <v>461.44873913043477</v>
       </c>
       <c r="E108">
         <v>394.7829565217391</v>
       </c>
       <c r="F108">
-        <v>2.521332485790141</v>
+        <v>2.5213324857901411</v>
       </c>
       <c r="G108">
         <v>15.01</v>
@@ -4200,10 +4228,10 @@
         <v>451.1675794833929</v>
       </c>
       <c r="I108">
-        <v>150.0712374549605</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
+        <v>150.07123745496051</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>116</v>
       </c>
@@ -4214,25 +4242,25 @@
         <v>242</v>
       </c>
       <c r="D109">
-        <v>447.9908571428572</v>
+        <v>447.99085714285718</v>
       </c>
       <c r="E109">
-        <v>389.0752857142857</v>
+        <v>389.07528571428571</v>
       </c>
       <c r="F109">
-        <v>2.529822030751787</v>
+        <v>2.5298220307517871</v>
       </c>
       <c r="G109">
         <v>15.31</v>
       </c>
       <c r="H109">
-        <v>456.1304228577102</v>
+        <v>456.13042285771019</v>
       </c>
       <c r="I109">
-        <v>151.4052053286892</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
+        <v>151.40520532868919</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>117</v>
       </c>
@@ -4243,25 +4271,25 @@
         <v>242</v>
       </c>
       <c r="D110">
-        <v>449.49545</v>
+        <v>449.49545000000001</v>
       </c>
       <c r="E110">
-        <v>381.36265</v>
+        <v>381.36264999999997</v>
       </c>
       <c r="F110">
-        <v>2.632429600454213</v>
+        <v>2.6324296004542131</v>
       </c>
       <c r="G110">
         <v>15.16</v>
       </c>
       <c r="H110">
-        <v>467.0775530062953</v>
+        <v>467.07755300629532</v>
       </c>
       <c r="I110">
         <v>146.4080176854722</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>118</v>
       </c>
@@ -4272,25 +4300,25 @@
         <v>242</v>
       </c>
       <c r="D111">
-        <v>478.7483</v>
+        <v>478.74829999999997</v>
       </c>
       <c r="E111">
-        <v>414.3545</v>
+        <v>414.35449999999997</v>
       </c>
       <c r="F111">
-        <v>2.516064167558619</v>
+        <v>2.5160641675586191</v>
       </c>
       <c r="G111">
         <v>15.75</v>
       </c>
       <c r="H111">
-        <v>474.550793854396</v>
+        <v>474.55079385439598</v>
       </c>
       <c r="I111">
         <v>149.7105856783669</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>119</v>
       </c>
@@ -4304,22 +4332,22 @@
         <v>494.1304761904762</v>
       </c>
       <c r="E112">
-        <v>405.9699047619048</v>
+        <v>405.96990476190479</v>
       </c>
       <c r="F112">
-        <v>2.493764714697909</v>
+        <v>2.4937647146979089</v>
       </c>
       <c r="G112">
         <v>16.47</v>
       </c>
       <c r="H112">
-        <v>480.2454033806488</v>
+        <v>480.24540338064878</v>
       </c>
       <c r="I112">
-        <v>154.6981207179059</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9">
+        <v>154.69812071790591</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>120</v>
       </c>
@@ -4330,25 +4358,25 @@
         <v>242</v>
       </c>
       <c r="D113">
-        <v>467.3595</v>
+        <v>467.35950000000003</v>
       </c>
       <c r="E113">
-        <v>388.9976</v>
+        <v>388.99759999999998</v>
       </c>
       <c r="F113">
-        <v>2.461148133424434</v>
+        <v>2.4611481334244338</v>
       </c>
       <c r="G113">
-        <v>16.24</v>
+        <v>16.239999999999998</v>
       </c>
       <c r="H113">
-        <v>486.4885936245972</v>
+        <v>486.48859362459717</v>
       </c>
       <c r="I113">
         <v>150.5802515362696</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>121</v>
       </c>
@@ -4359,10 +4387,10 @@
         <v>242</v>
       </c>
       <c r="D114">
-        <v>453.9553157894737</v>
+        <v>453.95531578947367</v>
       </c>
       <c r="E114">
-        <v>374.6515789473684</v>
+        <v>374.65157894736842</v>
       </c>
       <c r="F114">
         <v>2.349897228751884</v>
@@ -4371,13 +4399,13 @@
         <v>15.88</v>
       </c>
       <c r="H114">
-        <v>498.650808465212</v>
+        <v>498.65080846521198</v>
       </c>
       <c r="I114">
-        <v>143.6509908924644</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9">
+        <v>143.65099089246439</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>122</v>
       </c>
@@ -4388,10 +4416,10 @@
         <v>242</v>
       </c>
       <c r="D115">
-        <v>444.0977391304348</v>
+        <v>444.09773913043477</v>
       </c>
       <c r="E115">
-        <v>365.7765217391305</v>
+        <v>365.77652173913049</v>
       </c>
       <c r="F115">
         <v>2.316832641609115</v>
@@ -4400,13 +4428,13 @@
         <v>15.58</v>
       </c>
       <c r="H115">
-        <v>510.6184278683772</v>
+        <v>510.61842786837718</v>
       </c>
       <c r="I115">
-        <v>137.6339660555113</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9">
+        <v>137.63396605551131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>123</v>
       </c>
@@ -4417,25 +4445,25 @@
         <v>242</v>
       </c>
       <c r="D116">
-        <v>422.4111578947368</v>
+        <v>422.41115789473679</v>
       </c>
       <c r="E116">
-        <v>369.4322631578947</v>
+        <v>369.43226315789468</v>
       </c>
       <c r="F116">
-        <v>2.611329935326746</v>
+        <v>2.6113299353267458</v>
       </c>
       <c r="G116">
         <v>15.59</v>
       </c>
       <c r="H116">
-        <v>523.8945069929549</v>
+        <v>523.89450699295492</v>
       </c>
       <c r="I116">
-        <v>134.232267264563</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9">
+        <v>134.23226726456301</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>124</v>
       </c>
@@ -4446,25 +4474,25 @@
         <v>242</v>
       </c>
       <c r="D117">
-        <v>403.1280909090909</v>
+        <v>403.12809090909087</v>
       </c>
       <c r="E117">
-        <v>360.2988181818182</v>
+        <v>360.29881818181821</v>
       </c>
       <c r="F117">
-        <v>2.516899004922317</v>
+        <v>2.5168990049223172</v>
       </c>
       <c r="G117">
         <v>15.99</v>
       </c>
       <c r="H117">
-        <v>530.7051355838632</v>
+        <v>530.70513558386324</v>
       </c>
       <c r="I117">
         <v>135.9095044448066</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>125</v>
       </c>
@@ -4475,25 +4503,25 @@
         <v>242</v>
       </c>
       <c r="D118">
-        <v>410.0139090909091</v>
+        <v>410.01390909090912</v>
       </c>
       <c r="E118">
-        <v>367.0676818181818</v>
+        <v>367.06768181818182</v>
       </c>
       <c r="F118">
         <v>2.277803797344701</v>
       </c>
       <c r="G118">
-        <v>16.44</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="H118">
-        <v>537.0735972108697</v>
+        <v>537.07359721086971</v>
       </c>
       <c r="I118">
         <v>138.077420736813</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>126</v>
       </c>
@@ -4504,25 +4532,25 @@
         <v>242</v>
       </c>
       <c r="D119">
-        <v>436.1649</v>
+        <v>436.16489999999999</v>
       </c>
       <c r="E119">
-        <v>369.0248</v>
+        <v>369.02480000000003</v>
       </c>
       <c r="F119">
         <v>2.235447625020651</v>
       </c>
       <c r="G119">
-        <v>17.65</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="H119">
-        <v>546.2038483634544</v>
+        <v>546.20384836345443</v>
       </c>
       <c r="I119">
         <v>145.7620976253298</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>127</v>
       </c>
@@ -4533,25 +4561,25 @@
         <v>242</v>
       </c>
       <c r="D120">
-        <v>428.4211739130434</v>
+        <v>428.42117391304339</v>
       </c>
       <c r="E120">
-        <v>367.1506086956522</v>
+        <v>367.15060869565218</v>
       </c>
       <c r="F120">
-        <v>2.531797115696001</v>
+        <v>2.5317971156960009</v>
       </c>
       <c r="G120">
-        <v>17.83</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="H120">
-        <v>553.8507022405428</v>
+        <v>553.85070224054277</v>
       </c>
       <c r="I120">
-        <v>145.2156047996396</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9">
+        <v>145.21560479963961</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -4562,16 +4590,16 @@
         <v>242</v>
       </c>
       <c r="D121">
-        <v>388.48875</v>
+        <v>388.48874999999998</v>
       </c>
       <c r="E121">
-        <v>349.24675</v>
+        <v>349.24675000000002</v>
       </c>
       <c r="F121">
         <v>2.855032825637148</v>
       </c>
       <c r="G121">
-        <v>17.51</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="H121">
         <v>564.373865583113</v>
@@ -4580,7 +4608,7 @@
         <v>139.9503235519901</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>129</v>
       </c>
@@ -4591,25 +4619,25 @@
         <v>242</v>
       </c>
       <c r="D122">
-        <v>362.2950952380953</v>
+        <v>362.29509523809531</v>
       </c>
       <c r="E122">
-        <v>338.0442380952381</v>
+        <v>338.04423809523809</v>
       </c>
       <c r="F122">
-        <v>2.827621207762259</v>
+        <v>2.8276212077622591</v>
       </c>
       <c r="G122">
         <v>17.7</v>
       </c>
       <c r="H122">
-        <v>572.8394735668596</v>
+        <v>572.83947356685962</v>
       </c>
       <c r="I122">
-        <v>139.3782427983573</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9">
+        <v>139.37824279835729</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -4620,25 +4648,25 @@
         <v>242</v>
       </c>
       <c r="D123">
-        <v>370.3574761904762</v>
+        <v>370.35747619047618</v>
       </c>
       <c r="E123">
-        <v>347.9736666666666</v>
+        <v>347.97366666666659</v>
       </c>
       <c r="F123">
         <v>2.966698143781433</v>
       </c>
       <c r="G123">
-        <v>17.56</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="H123">
         <v>580.8592261967957</v>
       </c>
       <c r="I123">
-        <v>136.366682464656</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9">
+        <v>136.36668246465601</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>131</v>
       </c>
@@ -4649,25 +4677,25 @@
         <v>242</v>
       </c>
       <c r="D124">
-        <v>356.24895</v>
+        <v>356.24894999999998</v>
       </c>
       <c r="E124">
-        <v>344.5153</v>
+        <v>344.51530000000002</v>
       </c>
       <c r="F124">
-        <v>2.363455369001225</v>
+        <v>2.3634553690012252</v>
       </c>
       <c r="G124">
         <v>18.88</v>
       </c>
       <c r="H124">
-        <v>598.8658622088964</v>
+        <v>598.86586220889637</v>
       </c>
       <c r="I124">
-        <v>142.2090018610272</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9">
+        <v>142.20900186102719</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -4678,10 +4706,10 @@
         <v>242</v>
       </c>
       <c r="D125">
-        <v>364.6288095238095</v>
+        <v>364.62880952380948</v>
       </c>
       <c r="E125">
-        <v>332.5734285714286</v>
+        <v>332.57342857142862</v>
       </c>
       <c r="F125">
         <v>2.278398041910763</v>
@@ -4690,13 +4718,13 @@
         <v>19.55</v>
       </c>
       <c r="H125">
-        <v>609.6454477286564</v>
+        <v>609.64544772865645</v>
       </c>
       <c r="I125">
         <v>144.6518798482756</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -4707,10 +4735,10 @@
         <v>242</v>
       </c>
       <c r="D126">
-        <v>400.6435789473684</v>
+        <v>400.64357894736838</v>
       </c>
       <c r="E126">
-        <v>347.4308421052631</v>
+        <v>347.43084210526308</v>
       </c>
       <c r="F126">
         <v>2.320105810656333</v>
@@ -4719,13 +4747,13 @@
         <v>19.95</v>
       </c>
       <c r="H126">
-        <v>624.2769384741443</v>
+        <v>624.27693847414434</v>
       </c>
       <c r="I126">
         <v>144.1518643588704</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>134</v>
       </c>
@@ -4736,25 +4764,25 @@
         <v>242</v>
       </c>
       <c r="D127">
-        <v>412.0907142857143</v>
+        <v>412.09071428571428</v>
       </c>
       <c r="E127">
-        <v>354.3163809523809</v>
+        <v>354.31638095238088</v>
       </c>
       <c r="F127">
-        <v>2.321566881551839</v>
+        <v>2.3215668815518389</v>
       </c>
       <c r="G127">
         <v>20.36</v>
       </c>
       <c r="H127">
-        <v>638.6353080590495</v>
+        <v>638.63530805904952</v>
       </c>
       <c r="I127">
-        <v>143.8068268592596</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
+        <v>143.80682685925959</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>135</v>
       </c>
@@ -4765,10 +4793,10 @@
         <v>242</v>
       </c>
       <c r="D128">
-        <v>408.5527142857143</v>
+        <v>408.55271428571427</v>
       </c>
       <c r="E128">
-        <v>355.9704285714286</v>
+        <v>355.97042857142861</v>
       </c>
       <c r="F128">
         <v>2.065269766898731</v>
@@ -4777,13 +4805,13 @@
         <v>20.6</v>
       </c>
       <c r="H128">
-        <v>655.8784613766438</v>
+        <v>655.87846137664383</v>
       </c>
       <c r="I128">
-        <v>141.676724188595</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9">
+        <v>141.67672418859499</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>136</v>
       </c>
@@ -4794,10 +4822,10 @@
         <v>242</v>
       </c>
       <c r="D129">
-        <v>469.4827727272727</v>
+        <v>469.48277272727267</v>
       </c>
       <c r="E129">
-        <v>387.7447272727273</v>
+        <v>387.74472727272729</v>
       </c>
       <c r="F129">
         <v>1.937971326949482</v>
@@ -4806,13 +4834,13 @@
         <v>25.17</v>
       </c>
       <c r="H129">
-        <v>669.6519090655532</v>
+        <v>669.65190906555324</v>
       </c>
       <c r="I129">
         <v>169.5464729908303</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -4823,10 +4851,10 @@
         <v>242</v>
       </c>
       <c r="D130">
-        <v>529.1295714285714</v>
+        <v>529.12957142857135</v>
       </c>
       <c r="E130">
-        <v>407.9859047619047</v>
+        <v>407.98590476190469</v>
       </c>
       <c r="F130">
         <v>2.042160419513714</v>
@@ -4835,13 +4863,13 @@
         <v>28.4</v>
       </c>
       <c r="H130">
-        <v>694.4290297009786</v>
+        <v>694.42902970097862</v>
       </c>
       <c r="I130">
-        <v>184.4782320314276</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9">
+        <v>184.47823203142761</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>138</v>
       </c>
@@ -4855,7 +4883,7 @@
         <v>571.3922380952381</v>
       </c>
       <c r="E131">
-        <v>391.0232380952381</v>
+        <v>391.02323809523813</v>
       </c>
       <c r="F131">
         <v>2.01412257067296</v>
@@ -4864,13 +4892,13 @@
         <v>27.45</v>
       </c>
       <c r="H131">
-        <v>715.956329621709</v>
+        <v>715.95632962170896</v>
       </c>
       <c r="I131">
         <v>172.945979879465</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -4881,7 +4909,7 @@
         <v>242</v>
       </c>
       <c r="D132">
-        <v>668.4962608695653</v>
+        <v>668.49626086956528</v>
       </c>
       <c r="E132">
         <v>407.3036086956522</v>
@@ -4893,13 +4921,13 @@
         <v>36</v>
       </c>
       <c r="H132">
-        <v>743.8786264769556</v>
+        <v>743.87862647695556</v>
       </c>
       <c r="I132">
-        <v>218.3006735725903</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9">
+        <v>218.30067357259031</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -4910,25 +4938,25 @@
         <v>242</v>
       </c>
       <c r="D133">
-        <v>667.4912631578948</v>
+        <v>667.49126315789476</v>
       </c>
       <c r="E133">
-        <v>408.7607894736842</v>
+        <v>408.76078947368421</v>
       </c>
       <c r="F133">
         <v>1.749469585451281</v>
       </c>
       <c r="G133">
-        <v>39.3</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="H133">
-        <v>792.2307371979576</v>
+        <v>792.23073719795764</v>
       </c>
       <c r="I133">
-        <v>223.7667311268336</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9">
+        <v>223.76673112683361</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>141</v>
       </c>
@@ -4939,7 +4967,7 @@
         <v>242</v>
       </c>
       <c r="D134">
-        <v>658.1485454545455</v>
+        <v>658.14854545454546</v>
       </c>
       <c r="E134">
         <v>405.5604090909091</v>
@@ -4951,13 +4979,13 @@
         <v>34.5</v>
       </c>
       <c r="H134">
-        <v>835.0111970066473</v>
+        <v>835.01119700664731</v>
       </c>
       <c r="I134">
-        <v>186.372337149542</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9">
+        <v>186.37233714954201</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>142</v>
       </c>
@@ -4971,22 +4999,22 @@
         <v>655.79755</v>
       </c>
       <c r="E135">
-        <v>433.8635</v>
+        <v>433.86349999999999</v>
       </c>
       <c r="F135">
-        <v>1.767376686416854</v>
+        <v>1.7673766864168541</v>
       </c>
       <c r="G135">
         <v>36</v>
       </c>
       <c r="H135">
-        <v>861.7315553108602</v>
+        <v>861.73155531086024</v>
       </c>
       <c r="I135">
-        <v>188.4452347315895</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9">
+        <v>188.44523473158949</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>143</v>
       </c>
@@ -4997,10 +5025,10 @@
         <v>242</v>
       </c>
       <c r="D136">
-        <v>773.5672105263158</v>
+        <v>773.56721052631576</v>
       </c>
       <c r="E136">
-        <v>451.9626315789473</v>
+        <v>451.96263157894731</v>
       </c>
       <c r="F136">
         <v>1.92</v>
@@ -5009,13 +5037,13 @@
         <v>38.5</v>
       </c>
       <c r="H136">
-        <v>884.1365757489425</v>
+        <v>884.13657574894251</v>
       </c>
       <c r="I136">
-        <v>196.4246679977853</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9">
+        <v>196.42466799778529</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>144</v>
       </c>
@@ -5026,10 +5054,10 @@
         <v>242</v>
       </c>
       <c r="D137">
-        <v>700.9983333333333</v>
+        <v>700.99833333333333</v>
       </c>
       <c r="E137">
-        <v>428.5778095238095</v>
+        <v>428.57780952380949</v>
       </c>
       <c r="F137">
         <v>1.63</v>
@@ -5038,13 +5066,13 @@
         <v>35.5</v>
       </c>
       <c r="H137">
-        <v>909.7765364456617</v>
+        <v>909.77653644566169</v>
       </c>
       <c r="I137">
         <v>176.0144312072338</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>145</v>
       </c>
@@ -5055,25 +5083,25 @@
         <v>242</v>
       </c>
       <c r="D138">
-        <v>679.2966315789474</v>
+        <v>679.29663157894743</v>
       </c>
       <c r="E138">
-        <v>400.7199473684211</v>
+        <v>400.71994736842112</v>
       </c>
       <c r="F138">
         <v>1.79</v>
       </c>
       <c r="G138">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="H138">
         <v>944.3480448305969</v>
       </c>
       <c r="I138">
-        <v>185.3336571098448</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9">
+        <v>185.33365710984481</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>146</v>
       </c>
@@ -5087,7 +5115,7 @@
         <v>748.3870952380953</v>
       </c>
       <c r="E139">
-        <v>396.349380952381</v>
+        <v>396.34938095238101</v>
       </c>
       <c r="F139">
         <v>1.6</v>
@@ -5096,13 +5124,13 @@
         <v>42.65</v>
       </c>
       <c r="H139">
-        <v>988.732402937635</v>
+        <v>988.73240293763502</v>
       </c>
       <c r="I139">
-        <v>194.5785325705964</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9">
+        <v>194.57853257059639</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -5113,10 +5141,10 @@
         <v>242</v>
       </c>
       <c r="D140">
-        <v>838.9512857142856</v>
+        <v>838.95128571428563</v>
       </c>
       <c r="E140">
-        <v>390.7292380952381</v>
+        <v>390.72923809523809</v>
       </c>
       <c r="F140">
         <v>1.529328552142305</v>
@@ -5131,7 +5159,7 @@
         <v>198.5490728065659</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>148</v>
       </c>
@@ -5145,7 +5173,7 @@
         <v>924.9255454545455</v>
       </c>
       <c r="E141">
-        <v>408.1725</v>
+        <v>408.17250000000001</v>
       </c>
       <c r="F141">
         <v>1.614401720242761</v>
@@ -5154,13 +5182,13 @@
         <v>44.5</v>
       </c>
       <c r="H141">
-        <v>1054.042133081277</v>
+        <v>1054.0421330812769</v>
       </c>
       <c r="I141">
         <v>190.4393520830302</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>149</v>
       </c>
@@ -5171,25 +5199,25 @@
         <v>242</v>
       </c>
       <c r="D142">
-        <v>882.7601999999999</v>
+        <v>882.76019999999994</v>
       </c>
       <c r="E142">
-        <v>409.8799</v>
+        <v>409.87990000000002</v>
       </c>
       <c r="F142">
-        <v>1.856512266836157</v>
+        <v>1.8565122668361571</v>
       </c>
       <c r="G142">
         <v>42.3</v>
       </c>
       <c r="H142">
-        <v>1082.501270674472</v>
+        <v>1082.5012706744719</v>
       </c>
       <c r="I142">
-        <v>176.2652121508522</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9">
+        <v>176.26521215085219</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>150</v>
       </c>
@@ -5200,13 +5228,13 @@
         <v>242</v>
       </c>
       <c r="D143">
-        <v>789.6688181818182</v>
+        <v>789.66881818181821</v>
       </c>
       <c r="E143">
         <v>399.8</v>
       </c>
       <c r="F143">
-        <v>1.969687646569613</v>
+        <v>1.9696876465696129</v>
       </c>
       <c r="G143">
         <v>43.7</v>
@@ -5215,10 +5243,10 @@
         <v>1106.31629862931</v>
       </c>
       <c r="I143">
-        <v>178.1791085710641</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9">
+        <v>178.17910857106409</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>151</v>
       </c>
@@ -5232,22 +5260,22 @@
         <v>1568.443181818182</v>
       </c>
       <c r="E144">
-        <v>422.3191818181818</v>
+        <v>422.31918181818179</v>
       </c>
       <c r="F144">
-        <v>2.201439216228862</v>
+        <v>2.2014392162288621</v>
       </c>
       <c r="G144">
         <v>60</v>
       </c>
       <c r="H144">
-        <v>1150.568950574483</v>
+        <v>1150.5689505744831</v>
       </c>
       <c r="I144">
-        <v>235.2302964764972</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
+        <v>235.23029647649719</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -5258,10 +5286,10 @@
         <v>242</v>
       </c>
       <c r="D145">
-        <v>2169.6254</v>
+        <v>2169.6253999999999</v>
       </c>
       <c r="E145">
-        <v>401.57265</v>
+        <v>401.57265000000001</v>
       </c>
       <c r="F145">
         <v>1.91</v>
@@ -5270,13 +5298,13 @@
         <v>58.25</v>
       </c>
       <c r="H145">
-        <v>1218.452518658377</v>
+        <v>1218.4525186583769</v>
       </c>
       <c r="I145">
-        <v>215.6462821806101</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9">
+        <v>215.64628218061009</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>153</v>
       </c>
@@ -5290,22 +5318,22 @@
         <v>2107.811454545455</v>
       </c>
       <c r="E146">
-        <v>389.0283181818182</v>
+        <v>389.02831818181818</v>
       </c>
       <c r="F146">
-        <v>2.009021728810446</v>
+        <v>2.0090217288104459</v>
       </c>
       <c r="G146">
         <v>66</v>
       </c>
       <c r="H146">
-        <v>1258.661451774103</v>
+        <v>1258.6614517741029</v>
       </c>
       <c r="I146">
-        <v>236.5318668309772</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9">
+        <v>236.53186683097721</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -5316,13 +5344,13 @@
         <v>242</v>
       </c>
       <c r="D147">
-        <v>2336.261368421053</v>
+        <v>2336.2613684210528</v>
       </c>
       <c r="E147">
-        <v>373.0827894736842</v>
+        <v>373.08278947368422</v>
       </c>
       <c r="F147">
-        <v>1.97651878788223</v>
+        <v>1.9765187878822299</v>
       </c>
       <c r="G147">
         <v>66.25</v>
@@ -5331,10 +5359,10 @@
         <v>1312.78389420039</v>
       </c>
       <c r="I147">
-        <v>227.6393296951138</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9">
+        <v>227.63932969511379</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>155</v>
       </c>
@@ -5348,22 +5376,22 @@
         <v>2045.411095238095</v>
       </c>
       <c r="E148">
-        <v>330.1270952380953</v>
+        <v>330.12709523809531</v>
       </c>
       <c r="F148">
-        <v>1.967210147883227</v>
+        <v>1.9672101478832269</v>
       </c>
       <c r="G148">
         <v>73.5</v>
       </c>
       <c r="H148">
-        <v>1361.356898285804</v>
+        <v>1361.3568982858039</v>
       </c>
       <c r="I148">
         <v>243.5398298079127</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>156</v>
       </c>
@@ -5374,13 +5402,13 @@
         <v>241</v>
       </c>
       <c r="D149">
-        <v>1932.379952380952</v>
+        <v>1932.3799523809521</v>
       </c>
       <c r="E149">
-        <v>319.9605238095238</v>
+        <v>319.96052380952381</v>
       </c>
       <c r="F149">
-        <v>2.323353202071679</v>
+        <v>2.3233532020716789</v>
       </c>
       <c r="G149">
         <v>74</v>
@@ -5389,10 +5417,10 @@
         <v>1392.668106946378</v>
       </c>
       <c r="I149">
-        <v>239.6838351358954</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9">
+        <v>239.68383513589541</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>157</v>
       </c>
@@ -5406,22 +5434,22 @@
         <v>2017.343315789474</v>
       </c>
       <c r="E150">
-        <v>336.3139473684211</v>
+        <v>336.31394736842111</v>
       </c>
       <c r="F150">
-        <v>2.270241310964191</v>
+        <v>2.2702413109641908</v>
       </c>
       <c r="G150">
         <v>74.5</v>
       </c>
       <c r="H150">
-        <v>1420.521469085305</v>
+        <v>1420.5214690853049</v>
       </c>
       <c r="I150">
-        <v>236.5718828514071</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9">
+        <v>236.57188285140711</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>158</v>
       </c>
@@ -5432,25 +5460,25 @@
         <v>241</v>
       </c>
       <c r="D151">
-        <v>3375.817863636364</v>
+        <v>3375.8178636363641</v>
       </c>
       <c r="E151">
-        <v>578.1737272727273</v>
+        <v>578.17372727272732</v>
       </c>
       <c r="F151">
-        <v>2.218059196414037</v>
+        <v>2.2180591964140368</v>
       </c>
       <c r="G151">
         <v>78.5</v>
       </c>
       <c r="H151">
-        <v>1467.39867756512</v>
+        <v>1467.3986775651199</v>
       </c>
       <c r="I151">
-        <v>241.3104829724521</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9">
+        <v>241.31048297245209</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>159</v>
       </c>
@@ -5461,13 +5489,13 @@
         <v>241</v>
       </c>
       <c r="D152">
-        <v>3803.042714285714</v>
+        <v>3803.0427142857138</v>
       </c>
       <c r="E152">
-        <v>675.9801428571429</v>
+        <v>675.98014285714294</v>
       </c>
       <c r="F152">
-        <v>3.286881091591604</v>
+        <v>3.2868810915916038</v>
       </c>
       <c r="G152">
         <v>108</v>
@@ -5476,10 +5504,10 @@
         <v>1489.409657728597</v>
       </c>
       <c r="I152">
-        <v>327.0877244018051</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9">
+        <v>327.08772440180508</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>160</v>
       </c>
@@ -5490,13 +5518,13 @@
         <v>241</v>
       </c>
       <c r="D153">
-        <v>3003.4012</v>
+        <v>3003.4011999999998</v>
       </c>
       <c r="E153">
-        <v>600.9793</v>
+        <v>600.97929999999997</v>
       </c>
       <c r="F153">
-        <v>3.001746247597486</v>
+        <v>3.0017462475974859</v>
       </c>
       <c r="G153">
         <v>115</v>
@@ -5505,10 +5533,10 @@
         <v>1511.750802594526</v>
       </c>
       <c r="I153">
-        <v>343.1407435340959</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9">
+        <v>343.14074353409592</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>161</v>
       </c>
@@ -5519,13 +5547,13 @@
         <v>241</v>
       </c>
       <c r="D154">
-        <v>2538.557272727273</v>
+        <v>2538.5572727272729</v>
       </c>
       <c r="E154">
         <v>516.2921818181818</v>
       </c>
       <c r="F154">
-        <v>2.770225497216173</v>
+        <v>2.7702254972161731</v>
       </c>
       <c r="G154">
         <v>116</v>
@@ -5534,10 +5562,10 @@
         <v>1545.009320251605</v>
       </c>
       <c r="I154">
-        <v>338.6737535093604</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9">
+        <v>338.67375350936038</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -5548,25 +5576,25 @@
         <v>241</v>
       </c>
       <c r="D155">
-        <v>2322.409772727273</v>
+        <v>2322.4097727272729</v>
       </c>
       <c r="E155">
         <v>484.5533636363636</v>
       </c>
       <c r="F155">
-        <v>2.529596469176181</v>
+        <v>2.5295964691761812</v>
       </c>
       <c r="G155">
         <v>131</v>
       </c>
       <c r="H155">
-        <v>1574.364497336385</v>
+        <v>1574.3644973363851</v>
       </c>
       <c r="I155">
         <v>375.3363820998124</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>163</v>
       </c>
@@ -5580,10 +5608,10 @@
         <v>2119.03680952381</v>
       </c>
       <c r="E156">
-        <v>445.8940476190476</v>
+        <v>445.89404761904763</v>
       </c>
       <c r="F156">
-        <v>2.377857694087878</v>
+        <v>2.3778576940878779</v>
       </c>
       <c r="G156">
         <v>131</v>
@@ -5592,10 +5620,10 @@
         <v>1616.872338764467</v>
       </c>
       <c r="I156">
-        <v>365.4687264847249</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9">
+        <v>365.46872648472493</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>164</v>
       </c>
@@ -5609,22 +5637,22 @@
         <v>1504.97780952381</v>
       </c>
       <c r="E157">
-        <v>424.2365238095238</v>
+        <v>424.23652380952382</v>
       </c>
       <c r="F157">
-        <v>2.265968705449639</v>
+        <v>2.2659687054496391</v>
       </c>
       <c r="G157">
         <v>140</v>
       </c>
       <c r="H157">
-        <v>1662.144764249873</v>
+        <v>1662.1447642498731</v>
       </c>
       <c r="I157">
-        <v>379.9389736824002</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9">
+        <v>379.93897368240022</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>165</v>
       </c>
@@ -5635,10 +5663,10 @@
         <v>241</v>
       </c>
       <c r="D158">
-        <v>1409.394714285714</v>
+        <v>1409.3947142857139</v>
       </c>
       <c r="E158">
-        <v>415.1638571428572</v>
+        <v>415.16385714285718</v>
       </c>
       <c r="F158">
         <v>1.992343621116379</v>
@@ -5647,13 +5675,13 @@
         <v>163</v>
       </c>
       <c r="H158">
-        <v>1725.306265291368</v>
+        <v>1725.3062652913679</v>
       </c>
       <c r="I158">
-        <v>426.1633134477789</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9">
+        <v>426.16331344777888</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -5664,10 +5692,10 @@
         <v>241</v>
       </c>
       <c r="D159">
-        <v>1378.113789473684</v>
+        <v>1378.1137894736839</v>
       </c>
       <c r="E159">
-        <v>391.5335789473684</v>
+        <v>391.53357894736843</v>
       </c>
       <c r="F159">
         <v>2.019343321400906</v>
@@ -5676,13 +5704,13 @@
         <v>149</v>
       </c>
       <c r="H159">
-        <v>1780.516065780692</v>
+        <v>1780.5160657806921</v>
       </c>
       <c r="I159">
-        <v>377.480939409563</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9">
+        <v>377.48093940956301</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>167</v>
       </c>
@@ -5696,22 +5724,22 @@
         <v>1391.6025</v>
       </c>
       <c r="E160">
-        <v>369.6542727272727</v>
+        <v>369.65427272727271</v>
       </c>
       <c r="F160">
-        <v>1.853868186985875</v>
+        <v>1.8538681869858751</v>
       </c>
       <c r="G160">
         <v>160</v>
       </c>
       <c r="H160">
-        <v>1851.736708411919</v>
+        <v>1851.7367084119189</v>
       </c>
       <c r="I160">
-        <v>389.7583267006331</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9">
+        <v>389.75832670063312</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>168</v>
       </c>
@@ -5722,13 +5750,13 @@
         <v>241</v>
       </c>
       <c r="D161">
-        <v>1422.125631578947</v>
+        <v>1422.1256315789469</v>
       </c>
       <c r="E161">
-        <v>366.043052631579</v>
+        <v>366.04305263157897</v>
       </c>
       <c r="F161">
-        <v>1.87512971668241</v>
+        <v>1.8751297166824099</v>
       </c>
       <c r="G161">
         <v>148</v>
@@ -5737,10 +5765,10 @@
         <v>1925.806176748396</v>
       </c>
       <c r="I161">
-        <v>346.6600501904668</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9">
+        <v>346.66005019046679</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>169</v>
       </c>
@@ -5751,13 +5779,13 @@
         <v>241</v>
       </c>
       <c r="D162">
-        <v>1471.595947368421</v>
+        <v>1471.5959473684211</v>
       </c>
       <c r="E162">
-        <v>359.7951052631579</v>
+        <v>359.79510526315789</v>
       </c>
       <c r="F162">
-        <v>1.816565190227612</v>
+        <v>1.8165651902276121</v>
       </c>
       <c r="G162">
         <v>141</v>
@@ -5766,10 +5794,10 @@
         <v>1995.135199111339</v>
       </c>
       <c r="I162">
-        <v>318.7876126790659</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9">
+        <v>318.78761267906589</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>170</v>
       </c>
@@ -5780,25 +5808,25 @@
         <v>241</v>
       </c>
       <c r="D163">
-        <v>1568.114869565217</v>
+        <v>1568.1148695652171</v>
       </c>
       <c r="E163">
-        <v>370.9023913043479</v>
+        <v>370.90239130434787</v>
       </c>
       <c r="F163">
-        <v>1.783856411282359</v>
+        <v>1.7838564112823589</v>
       </c>
       <c r="G163">
         <v>136</v>
       </c>
       <c r="H163">
-        <v>2090.901688668683</v>
+        <v>2090.9016886686832</v>
       </c>
       <c r="I163">
-        <v>293.399892563701</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9">
+        <v>293.39989256370097</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -5815,19 +5843,19 @@
         <v>349.5269090909091</v>
       </c>
       <c r="F164">
-        <v>1.732997555083391</v>
+        <v>1.7329975550833909</v>
       </c>
       <c r="G164">
         <v>145</v>
       </c>
       <c r="H164">
-        <v>2176.628657904099</v>
+        <v>2176.6286579040989</v>
       </c>
       <c r="I164">
-        <v>300.495736719053</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9">
+        <v>300.49573671905301</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>172</v>
       </c>
@@ -5838,25 +5866,25 @@
         <v>241</v>
       </c>
       <c r="D165">
-        <v>1547.93315</v>
+        <v>1547.9331500000001</v>
       </c>
       <c r="E165">
-        <v>340.4156</v>
+        <v>340.41559999999998</v>
       </c>
       <c r="F165">
-        <v>1.932056505048854</v>
+        <v>1.9320565050488541</v>
       </c>
       <c r="G165">
         <v>152</v>
       </c>
       <c r="H165">
-        <v>2248.457403614934</v>
+        <v>2248.4574036149338</v>
       </c>
       <c r="I165">
-        <v>304.9394263864609</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9">
+        <v>304.93942638646092</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>173</v>
       </c>
@@ -5867,10 +5895,10 @@
         <v>241</v>
       </c>
       <c r="D166">
-        <v>1514.253409090909</v>
+        <v>1514.2534090909089</v>
       </c>
       <c r="E166">
-        <v>342.8785909090909</v>
+        <v>342.87859090909092</v>
       </c>
       <c r="F166">
         <v>1.703405468541608</v>
@@ -5879,13 +5907,13 @@
         <v>163</v>
       </c>
       <c r="H166">
-        <v>2320.408040530612</v>
+        <v>2320.4080405306122</v>
       </c>
       <c r="I166">
-        <v>316.8676465026592</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9">
+        <v>316.86764650265923</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>174</v>
       </c>
@@ -5896,10 +5924,10 @@
         <v>241</v>
       </c>
       <c r="D167">
-        <v>1596.668380952381</v>
+        <v>1596.6683809523811</v>
       </c>
       <c r="E167">
-        <v>360.8981428571428</v>
+        <v>360.89814285714277</v>
       </c>
       <c r="F167">
         <v>1.698241844452488</v>
@@ -5908,13 +5936,13 @@
         <v>175.5</v>
       </c>
       <c r="H167">
-        <v>2390.020281746531</v>
+        <v>2390.0202817465311</v>
       </c>
       <c r="I167">
-        <v>331.2304006267001</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9">
+        <v>331.23040062670009</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>175</v>
       </c>
@@ -5928,22 +5956,22 @@
         <v>1566.825636363636</v>
       </c>
       <c r="E168">
-        <v>365.0310909090909</v>
+        <v>365.03109090909089</v>
       </c>
       <c r="F168">
-        <v>1.852228137348343</v>
+        <v>1.8522281373483429</v>
       </c>
       <c r="G168">
         <v>176.5</v>
       </c>
       <c r="H168">
-        <v>2449.770788790194</v>
+        <v>2449.7707887901938</v>
       </c>
       <c r="I168">
-        <v>324.9929300847061</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9">
+        <v>324.99293008470607</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>176</v>
       </c>
@@ -5954,13 +5982,13 @@
         <v>241</v>
       </c>
       <c r="D169">
-        <v>1543.657</v>
+        <v>1543.6569999999999</v>
       </c>
       <c r="E169">
-        <v>362.682619047619</v>
+        <v>362.68261904761903</v>
       </c>
       <c r="F169">
-        <v>1.579327806942728</v>
+        <v>1.5793278069427279</v>
       </c>
       <c r="G169">
         <v>182</v>
@@ -5969,10 +5997,10 @@
         <v>2535.512766397851</v>
       </c>
       <c r="I169">
-        <v>323.7876217674126</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9">
+        <v>323.78762176741259</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>177</v>
       </c>
@@ -5995,13 +6023,13 @@
         <v>193.5</v>
       </c>
       <c r="H170">
-        <v>2624.255713221775</v>
+        <v>2624.2557132217748</v>
       </c>
       <c r="I170">
-        <v>332.6055359770364</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9">
+        <v>332.60553597703642</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>178</v>
       </c>
@@ -6012,25 +6040,25 @@
         <v>241</v>
       </c>
       <c r="D171">
-        <v>1763.5622</v>
+        <v>1763.5622000000001</v>
       </c>
       <c r="E171">
-        <v>381.6926</v>
+        <v>381.69260000000003</v>
       </c>
       <c r="F171">
-        <v>1.453584417495111</v>
+        <v>1.4535844174951109</v>
       </c>
       <c r="G171">
         <v>197.5</v>
       </c>
       <c r="H171">
-        <v>2689.862106052319</v>
+        <v>2689.8621060523192</v>
       </c>
       <c r="I171">
-        <v>331.2010757192397</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9">
+        <v>331.20107571923973</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>179</v>
       </c>
@@ -6044,7 +6072,7 @@
         <v>1728.903818181818</v>
       </c>
       <c r="E172">
-        <v>385.8482727272727</v>
+        <v>385.84827272727267</v>
       </c>
       <c r="F172">
         <v>1.422823400279098</v>
@@ -6053,13 +6081,13 @@
         <v>204</v>
       </c>
       <c r="H172">
-        <v>2792.076866082307</v>
+        <v>2792.0768660823069</v>
       </c>
       <c r="I172">
-        <v>329.577422242018</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9">
+        <v>329.57742224201797</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>180</v>
       </c>
@@ -6070,25 +6098,25 @@
         <v>241</v>
       </c>
       <c r="D173">
-        <v>1838.01245</v>
+        <v>1838.0124499999999</v>
       </c>
       <c r="E173">
-        <v>389.20895</v>
+        <v>389.20895000000002</v>
       </c>
       <c r="F173">
-        <v>1.54380817168773</v>
+        <v>1.5438081716877301</v>
       </c>
       <c r="G173">
         <v>209</v>
       </c>
       <c r="H173">
-        <v>2900.967863859517</v>
+        <v>2900.9678638595169</v>
       </c>
       <c r="I173">
-        <v>324.981039690227</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9">
+        <v>324.98103969022702</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>181</v>
       </c>
@@ -6099,10 +6127,10 @@
         <v>241</v>
       </c>
       <c r="D174">
-        <v>1764.322421052632</v>
+        <v>1764.3224210526321</v>
       </c>
       <c r="E174">
-        <v>398.6293684210526</v>
+        <v>398.62936842105262</v>
       </c>
       <c r="F174">
         <v>1.494020574046969</v>
@@ -6111,13 +6139,13 @@
         <v>207</v>
       </c>
       <c r="H174">
-        <v>3037.313353460915</v>
+        <v>3037.3133534609151</v>
       </c>
       <c r="I174">
         <v>307.4223240512971</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -6131,7 +6159,7 @@
         <v>1819.187391304348</v>
       </c>
       <c r="E175">
-        <v>412.5070869565217</v>
+        <v>412.50708695652168</v>
       </c>
       <c r="F175">
         <v>1.507731000735945</v>
@@ -6140,13 +6168,13 @@
         <v>196</v>
       </c>
       <c r="H175">
-        <v>3240.813348142796</v>
+        <v>3240.8133481427958</v>
       </c>
       <c r="I175">
-        <v>272.8077526228409</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9">
+        <v>272.80775262284089</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>183</v>
       </c>
@@ -6157,25 +6185,25 @@
         <v>241</v>
       </c>
       <c r="D176">
-        <v>1728.30415</v>
+        <v>1728.3041499999999</v>
       </c>
       <c r="E176">
         <v>393.00995</v>
       </c>
       <c r="F176">
-        <v>1.436073212958615</v>
+        <v>1.4360732129586149</v>
       </c>
       <c r="G176">
         <v>196.5</v>
       </c>
       <c r="H176">
-        <v>3435.262149031364</v>
+        <v>3435.2621490313641</v>
       </c>
       <c r="I176">
-        <v>258.0223497804593</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9">
+        <v>258.02234978045931</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -6186,25 +6214,25 @@
         <v>241</v>
       </c>
       <c r="D177">
-        <v>1881.78319047619</v>
+        <v>1881.7831904761899</v>
       </c>
       <c r="E177">
-        <v>434.6852857142857</v>
+        <v>434.68528571428573</v>
       </c>
       <c r="F177">
-        <v>1.303236155495347</v>
+        <v>1.3032361554953471</v>
       </c>
       <c r="G177">
         <v>201</v>
       </c>
       <c r="H177">
-        <v>3610.460518631963</v>
+        <v>3610.4605186319632</v>
       </c>
       <c r="I177">
         <v>251.123937729836</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>185</v>
       </c>
@@ -6218,7 +6246,7 @@
         <v>2150.381571428572</v>
       </c>
       <c r="E178">
-        <v>457.2629523809524</v>
+        <v>457.26295238095241</v>
       </c>
       <c r="F178">
         <v>1.401615678404754</v>
@@ -6227,13 +6255,13 @@
         <v>234</v>
       </c>
       <c r="H178">
-        <v>3801.814926119457</v>
+        <v>3801.8149261194571</v>
       </c>
       <c r="I178">
-        <v>277.6384054503438</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9">
+        <v>277.63840545034378</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>186</v>
       </c>
@@ -6244,25 +6272,25 @@
         <v>241</v>
       </c>
       <c r="D179">
-        <v>2701.9711</v>
+        <v>2701.9711000000002</v>
       </c>
       <c r="E179">
-        <v>516.3936</v>
+        <v>516.39359999999999</v>
       </c>
       <c r="F179">
-        <v>1.116666795145642</v>
+        <v>1.1166667951456419</v>
       </c>
       <c r="G179">
         <v>286</v>
       </c>
       <c r="H179">
-        <v>4083.149230652297</v>
+        <v>4083.1492306522969</v>
       </c>
       <c r="I179">
-        <v>315.9551479364558</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9">
+        <v>315.95514793645577</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>187</v>
       </c>
@@ -6273,10 +6301,10 @@
         <v>241</v>
       </c>
       <c r="D180">
-        <v>2417.345043478261</v>
+        <v>2417.3450434782608</v>
       </c>
       <c r="E180">
-        <v>470.4875652173913</v>
+        <v>470.48756521739131</v>
       </c>
       <c r="F180">
         <v>1.182576708825783</v>
@@ -6285,13 +6313,13 @@
         <v>285</v>
       </c>
       <c r="H180">
-        <v>4368.969676797959</v>
+        <v>4368.9696767979594</v>
       </c>
       <c r="I180">
-        <v>294.2527193055679</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9">
+        <v>294.25271930556789</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -6302,10 +6330,10 @@
         <v>241</v>
       </c>
       <c r="D181">
-        <v>2450.371238095238</v>
+        <v>2450.3712380952379</v>
       </c>
       <c r="E181">
-        <v>485.9667142857143</v>
+        <v>485.96671428571432</v>
       </c>
       <c r="F181">
         <v>1.230554148277315</v>
@@ -6314,13 +6342,13 @@
         <v>284</v>
       </c>
       <c r="H181">
-        <v>4639.845796759432</v>
+        <v>4639.8457967594322</v>
       </c>
       <c r="I181">
-        <v>276.101933732386</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9">
+        <v>276.10193373238599</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>189</v>
       </c>
@@ -6331,13 +6359,13 @@
         <v>241</v>
       </c>
       <c r="D182">
-        <v>2707.6944</v>
+        <v>2707.6943999999999</v>
       </c>
       <c r="E182">
-        <v>511.5483</v>
+        <v>511.54829999999998</v>
       </c>
       <c r="F182">
-        <v>1.281744966868246</v>
+        <v>1.2817449668682459</v>
       </c>
       <c r="G182">
         <v>286</v>
@@ -6349,7 +6377,7 @@
         <v>261.5675574293536</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -6360,25 +6388,25 @@
         <v>241</v>
       </c>
       <c r="D183">
-        <v>2443.5202</v>
+        <v>2443.5201999999999</v>
       </c>
       <c r="E183">
-        <v>455.45655</v>
+        <v>455.45654999999999</v>
       </c>
       <c r="F183">
-        <v>1.18955304112193</v>
+        <v>1.1895530411219299</v>
       </c>
       <c r="G183">
         <v>310</v>
       </c>
       <c r="H183">
-        <v>5173.831729971083</v>
+        <v>5173.8317299710834</v>
       </c>
       <c r="I183">
-        <v>270.2738632300481</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9">
+        <v>270.27386323004811</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>191</v>
       </c>
@@ -6392,7 +6420,7 @@
         <v>2218.813714285714</v>
       </c>
       <c r="E184">
-        <v>423.9385238095238</v>
+        <v>423.93852380952382</v>
       </c>
       <c r="F184">
         <v>1.251266302623613</v>
@@ -6401,13 +6429,13 @@
         <v>342</v>
       </c>
       <c r="H184">
-        <v>5437.697148199609</v>
+        <v>5437.6971481996088</v>
       </c>
       <c r="I184">
-        <v>283.7041871786515</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9">
+        <v>283.70418717865152</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>192</v>
       </c>
@@ -6418,25 +6446,25 @@
         <v>241</v>
       </c>
       <c r="D185">
-        <v>1949.8928</v>
+        <v>1949.8928000000001</v>
       </c>
       <c r="E185">
-        <v>408.2787</v>
+        <v>408.27870000000001</v>
       </c>
       <c r="F185">
-        <v>1.274121460945565</v>
+        <v>1.2741214609455651</v>
       </c>
       <c r="G185">
         <v>379</v>
       </c>
       <c r="H185">
-        <v>5763.958977091585</v>
+        <v>5763.9589770915854</v>
       </c>
       <c r="I185">
-        <v>296.6012549396141</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9">
+        <v>296.60125493961408</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>193</v>
       </c>
@@ -6447,10 +6475,10 @@
         <v>241</v>
       </c>
       <c r="D186">
-        <v>1966.012157894737</v>
+        <v>1966.0121578947369</v>
       </c>
       <c r="E186">
-        <v>408.0571578947369</v>
+        <v>408.05715789473692</v>
       </c>
       <c r="F186">
         <v>1.171329943690566</v>
@@ -6459,13 +6487,13 @@
         <v>373</v>
       </c>
       <c r="H186">
-        <v>6144.38026957963</v>
+        <v>6144.3802695796303</v>
       </c>
       <c r="I186">
-        <v>273.8327584996462</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9">
+        <v>273.83275849964622</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>194</v>
       </c>
@@ -6476,25 +6504,25 @@
         <v>241</v>
       </c>
       <c r="D187">
-        <v>2292.256739130435</v>
+        <v>2292.2567391304351</v>
       </c>
       <c r="E187">
-        <v>445.5204347826087</v>
+        <v>445.52043478260867</v>
       </c>
       <c r="F187">
-        <v>1.177622123271976</v>
+        <v>1.1776221232719759</v>
       </c>
       <c r="G187">
         <v>388</v>
       </c>
       <c r="H187">
-        <v>6617.497550337263</v>
+        <v>6617.4975503372634</v>
       </c>
       <c r="I187">
-        <v>264.4798511849336</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9">
+        <v>264.47985118493358</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>195</v>
       </c>
@@ -6505,10 +6533,10 @@
         <v>241</v>
       </c>
       <c r="D188">
-        <v>2501.57115</v>
+        <v>2501.5711500000002</v>
       </c>
       <c r="E188">
-        <v>449.89415</v>
+        <v>449.89415000000002</v>
       </c>
       <c r="F188">
         <v>1.070521319337423</v>
@@ -6517,13 +6545,13 @@
         <v>462</v>
       </c>
       <c r="H188">
-        <v>7173.367344565592</v>
+        <v>7173.3673445655922</v>
       </c>
       <c r="I188">
-        <v>290.5183437807646</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9">
+        <v>290.51834378076461</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>196</v>
       </c>
@@ -6534,10 +6562,10 @@
         <v>241</v>
       </c>
       <c r="D189">
-        <v>2575.878590909091</v>
+        <v>2575.8785909090911</v>
       </c>
       <c r="E189">
-        <v>444.096409090909</v>
+        <v>444.09640909090899</v>
       </c>
       <c r="F189">
         <v>1.132271190269593</v>
@@ -6549,10 +6577,10 @@
         <v>7732.88999744171</v>
       </c>
       <c r="I189">
-        <v>282.9140799734774</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9">
+        <v>282.91407997347739</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>197</v>
       </c>
@@ -6563,25 +6591,25 @@
         <v>241</v>
       </c>
       <c r="D190">
-        <v>2299.088428571429</v>
+        <v>2299.0884285714292</v>
       </c>
       <c r="E190">
-        <v>415.1874285714285</v>
+        <v>415.18742857142848</v>
       </c>
       <c r="F190">
-        <v>1.119683705893496</v>
+        <v>1.1196837058934961</v>
       </c>
       <c r="G190">
         <v>489</v>
       </c>
       <c r="H190">
-        <v>8196.863397288213</v>
+        <v>8196.8633972882126</v>
       </c>
       <c r="I190">
-        <v>269.1013131823195</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9">
+        <v>269.10131318231947</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>198</v>
       </c>
@@ -6598,19 +6626,19 @@
         <v>388.73415</v>
       </c>
       <c r="F191">
-        <v>1.199</v>
+        <v>1.1990000000000001</v>
       </c>
       <c r="G191">
         <v>545</v>
       </c>
       <c r="H191">
-        <v>8713.26579131737</v>
+        <v>8713.2657913173698</v>
       </c>
       <c r="I191">
-        <v>282.1435949965355</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9">
+        <v>282.14359499653551</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -6624,7 +6652,7 @@
         <v>2053.344130434783</v>
       </c>
       <c r="E192">
-        <v>386.1735217391304</v>
+        <v>386.17352173913042</v>
       </c>
       <c r="F192">
         <v>1.266</v>
@@ -6633,13 +6661,13 @@
         <v>725</v>
       </c>
       <c r="H192">
-        <v>9793.710749440725</v>
+        <v>9793.7107494407246</v>
       </c>
       <c r="I192">
-        <v>333.9222736173041</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9">
+        <v>333.92227361730409</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>200</v>
       </c>
@@ -6650,13 +6678,13 @@
         <v>241</v>
       </c>
       <c r="D193">
-        <v>2247.5088</v>
+        <v>2247.5088000000001</v>
       </c>
       <c r="E193">
-        <v>391.0261</v>
+        <v>391.02609999999999</v>
       </c>
       <c r="F193">
-        <v>1.032258890168475</v>
+        <v>1.0322588901684751</v>
       </c>
       <c r="G193">
         <v>790</v>
@@ -6665,10 +6693,10 @@
         <v>11037.5120146197</v>
       </c>
       <c r="I193">
-        <v>322.8572605423863</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9">
+        <v>322.85726054238631</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>201</v>
       </c>
@@ -6679,13 +6707,13 @@
         <v>241</v>
       </c>
       <c r="D194">
-        <v>2540.277952380952</v>
+        <v>2540.2779523809518</v>
       </c>
       <c r="E194">
-        <v>413.9241428571428</v>
+        <v>413.92414285714278</v>
       </c>
       <c r="F194">
-        <v>1.222760093842488</v>
+        <v>1.2227600938424881</v>
       </c>
       <c r="G194">
         <v>870</v>
@@ -6694,10 +6722,10 @@
         <v>11953.62551183313</v>
       </c>
       <c r="I194">
-        <v>328.3025546382834</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9">
+        <v>328.30255463828342</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>202</v>
       </c>
@@ -6708,13 +6736,13 @@
         <v>241</v>
       </c>
       <c r="D195">
-        <v>2327.432285714286</v>
+        <v>2327.4322857142861</v>
       </c>
       <c r="E195">
         <v>402.07</v>
       </c>
       <c r="F195">
-        <v>1.413952379948812</v>
+        <v>1.4139523799488121</v>
       </c>
       <c r="G195">
         <v>855</v>
@@ -6723,10 +6751,10 @@
         <v>13483.68957734777</v>
       </c>
       <c r="I195">
-        <v>286.0302887989446</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9">
+        <v>286.03028879894458</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -6737,25 +6765,25 @@
         <v>242</v>
       </c>
       <c r="D196">
-        <v>1888.6987</v>
+        <v>1888.6986999999999</v>
       </c>
       <c r="E196">
-        <v>373.1616</v>
+        <v>373.16160000000002</v>
       </c>
       <c r="F196">
-        <v>2.858223831865991</v>
+        <v>2.8582238318659909</v>
       </c>
       <c r="G196">
         <v>975</v>
       </c>
       <c r="H196">
-        <v>16922.03041957145</v>
+        <v>16922.030419571449</v>
       </c>
       <c r="I196">
         <v>259.9003113431383</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>204</v>
       </c>
@@ -6769,7 +6797,7 @@
         <v>1948.955809523809</v>
       </c>
       <c r="E197">
-        <v>377.7064285714285</v>
+        <v>377.70642857142849</v>
       </c>
       <c r="F197">
         <v>2.609779887415379</v>
@@ -6781,10 +6809,10 @@
         <v>20407.96868600318</v>
       </c>
       <c r="I197">
-        <v>253.0814784946153</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9">
+        <v>253.08147849461531</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>205</v>
       </c>
@@ -6795,13 +6823,13 @@
         <v>242</v>
       </c>
       <c r="D198">
-        <v>1848.6364</v>
+        <v>1848.6364000000001</v>
       </c>
       <c r="E198">
-        <v>361.70895</v>
+        <v>361.70895000000002</v>
       </c>
       <c r="F198">
-        <v>2.572334726168444</v>
+        <v>2.5723347261684442</v>
       </c>
       <c r="G198">
         <v>1000</v>
@@ -6810,10 +6838,10 @@
         <v>23101.8205525556</v>
       </c>
       <c r="I198">
-        <v>195.2578259251433</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9">
+        <v>195.25782592514329</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>206</v>
       </c>
@@ -6824,13 +6852,13 @@
         <v>242</v>
       </c>
       <c r="D199">
-        <v>1557.11415</v>
+        <v>1557.1141500000001</v>
       </c>
       <c r="E199">
-        <v>336.6853</v>
+        <v>336.68529999999998</v>
       </c>
       <c r="F199">
-        <v>2.560638873499365</v>
+        <v>2.5606388734993648</v>
       </c>
       <c r="G199">
         <v>980</v>
@@ -6839,10 +6867,10 @@
         <v>25643.02081333672</v>
       </c>
       <c r="I199">
-        <v>172.3897922582346</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9">
+        <v>172.38979225823459</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>207</v>
       </c>
@@ -6856,22 +6884,22 @@
         <v>1282.941954545455</v>
       </c>
       <c r="E200">
-        <v>322.8476363636364</v>
+        <v>322.84763636363641</v>
       </c>
       <c r="F200">
-        <v>2.448938405117059</v>
+        <v>2.4489384051170591</v>
       </c>
       <c r="G200">
         <v>1010</v>
       </c>
       <c r="H200">
-        <v>27899.60664491035</v>
+        <v>27899.606644910349</v>
       </c>
       <c r="I200">
-        <v>163.2969033058382</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9">
+        <v>163.29690330583821</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>208</v>
       </c>
@@ -6885,22 +6913,22 @@
         <v>1289.092272727273</v>
       </c>
       <c r="E201">
-        <v>411.275</v>
+        <v>411.27499999999998</v>
       </c>
       <c r="F201">
-        <v>2.514</v>
+        <v>2.5139999999999998</v>
       </c>
       <c r="G201">
         <v>1195</v>
       </c>
       <c r="H201">
-        <v>29071.39012399659</v>
+        <v>29071.390123996589</v>
       </c>
       <c r="I201">
-        <v>185.4200789138145</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9">
+        <v>185.42007891381451</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>209</v>
       </c>
@@ -6917,19 +6945,19 @@
         <v>457.9487894736842</v>
       </c>
       <c r="F202">
-        <v>2.462</v>
+        <v>2.4620000000000002</v>
       </c>
       <c r="G202">
         <v>1335</v>
       </c>
       <c r="H202">
-        <v>30408.67406970043</v>
+        <v>30408.674069700432</v>
       </c>
       <c r="I202">
         <v>198.0333970814838</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>210</v>
       </c>
@@ -6940,10 +6968,10 @@
         <v>242</v>
       </c>
       <c r="D203">
-        <v>1535.540863636364</v>
+        <v>1535.5408636363641</v>
       </c>
       <c r="E203">
-        <v>469.0511818181818</v>
+        <v>469.05118181818182</v>
       </c>
       <c r="F203">
         <v>2.371791659866759</v>
@@ -6955,10 +6983,10 @@
         <v>31625.02103248845</v>
       </c>
       <c r="I203">
-        <v>191.1298992287441</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9">
+        <v>191.12989922874411</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>211</v>
       </c>
@@ -6969,25 +6997,25 @@
         <v>242</v>
       </c>
       <c r="D204">
-        <v>1529.616863636364</v>
+        <v>1529.6168636363641</v>
       </c>
       <c r="E204">
-        <v>477.6136363636364</v>
+        <v>477.61363636363637</v>
       </c>
       <c r="F204">
-        <v>2.537232815002046</v>
+        <v>2.5372328150020458</v>
       </c>
       <c r="G204">
         <v>1275</v>
       </c>
       <c r="H204">
-        <v>32953.27191585297</v>
+        <v>32953.271915852973</v>
       </c>
       <c r="I204">
         <v>174.5284767501137</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>212</v>
       </c>
@@ -6998,10 +7026,10 @@
         <v>242</v>
       </c>
       <c r="D205">
-        <v>1377.2731</v>
+        <v>1377.2731000000001</v>
       </c>
       <c r="E205">
-        <v>462.5483</v>
+        <v>462.54829999999998</v>
       </c>
       <c r="F205">
         <v>2.160839974385047</v>
@@ -7010,13 +7038,13 @@
         <v>1205</v>
       </c>
       <c r="H205">
-        <v>34106.63643290782</v>
+        <v>34106.636432907821</v>
       </c>
       <c r="I205">
         <v>159.3686194819642</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>213</v>
       </c>
@@ -7027,25 +7055,25 @@
         <v>242</v>
       </c>
       <c r="D206">
-        <v>1099.463318181818</v>
+        <v>1099.4633181818181</v>
       </c>
       <c r="E206">
-        <v>432.2132727272727</v>
+        <v>432.21327272727268</v>
       </c>
       <c r="F206">
-        <v>2.425</v>
+        <v>2.4249999999999998</v>
       </c>
       <c r="G206">
         <v>1150</v>
       </c>
       <c r="H206">
-        <v>35027.51561659633</v>
+        <v>35027.515616596327</v>
       </c>
       <c r="I206">
-        <v>148.0959426636489</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9">
+        <v>148.09594266364891</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>214</v>
       </c>
@@ -7056,25 +7084,25 @@
         <v>242</v>
       </c>
       <c r="D207">
-        <v>805.2621578947368</v>
+        <v>805.26215789473679</v>
       </c>
       <c r="E207">
-        <v>426.4770526315789</v>
+        <v>426.47705263157889</v>
       </c>
       <c r="F207">
-        <v>2.664</v>
+        <v>2.6640000000000001</v>
       </c>
       <c r="G207">
         <v>1090</v>
       </c>
       <c r="H207">
-        <v>35868.17599139465</v>
+        <v>35868.175991394652</v>
       </c>
       <c r="I207">
-        <v>137.079294754906</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9">
+        <v>137.07929475490599</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>215</v>
       </c>
@@ -7085,25 +7113,25 @@
         <v>242</v>
       </c>
       <c r="D208">
-        <v>693.4795238095238</v>
+        <v>693.47952380952381</v>
       </c>
       <c r="E208">
         <v>423.544380952381</v>
       </c>
       <c r="F208">
-        <v>2.655</v>
+        <v>2.6549999999999998</v>
       </c>
       <c r="G208">
         <v>1195</v>
       </c>
       <c r="H208">
-        <v>36836.6167431623</v>
+        <v>36836.616743162303</v>
       </c>
       <c r="I208">
-        <v>146.3331849531571</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9">
+        <v>146.33318495315709</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>216</v>
       </c>
@@ -7114,10 +7142,10 @@
         <v>242</v>
       </c>
       <c r="D209">
-        <v>606.2395714285714</v>
+        <v>606.23957142857137</v>
       </c>
       <c r="E209">
-        <v>418.0773333333333</v>
+        <v>418.07733333333329</v>
       </c>
       <c r="F209">
         <v>2.605</v>
@@ -7126,13 +7154,13 @@
         <v>1200</v>
       </c>
       <c r="H209">
-        <v>37647.02231151186</v>
+        <v>37647.022311511857</v>
       </c>
       <c r="I209">
         <v>143.7822482324334</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>217</v>
       </c>
@@ -7143,25 +7171,25 @@
         <v>242</v>
       </c>
       <c r="D210">
-        <v>699.3476842105263</v>
+        <v>699.34768421052627</v>
       </c>
       <c r="E210">
-        <v>416.0381578947369</v>
+        <v>416.03815789473691</v>
       </c>
       <c r="F210">
-        <v>2.558</v>
+        <v>2.5579999999999998</v>
       </c>
       <c r="G210">
         <v>1210</v>
       </c>
       <c r="H210">
-        <v>38550.55084698815</v>
+        <v>38550.550846988153</v>
       </c>
       <c r="I210">
-        <v>141.5824547210648</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9">
+        <v>141.58245472106481</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>218</v>
       </c>
@@ -7172,10 +7200,10 @@
         <v>242</v>
       </c>
       <c r="D211">
-        <v>750.8911428571429</v>
+        <v>750.89114285714288</v>
       </c>
       <c r="E211">
-        <v>430.1711904761904</v>
+        <v>430.17119047619042</v>
       </c>
       <c r="F211">
         <v>2.42</v>
@@ -7184,13 +7212,13 @@
         <v>1280</v>
       </c>
       <c r="H211">
-        <v>39976.9212283267</v>
+        <v>39976.921228326697</v>
       </c>
       <c r="I211">
-        <v>144.429291458166</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9">
+        <v>144.42929145816601</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>219</v>
       </c>
@@ -7201,10 +7229,10 @@
         <v>242</v>
       </c>
       <c r="D212">
-        <v>790.8106190476191</v>
+        <v>790.81061904761907</v>
       </c>
       <c r="E212">
-        <v>460.4033333333333</v>
+        <v>460.40333333333331</v>
       </c>
       <c r="F212">
         <v>2.331</v>
@@ -7213,13 +7241,13 @@
         <v>1180</v>
       </c>
       <c r="H212">
-        <v>41096.27502271986</v>
+        <v>41096.275022719863</v>
       </c>
       <c r="I212">
         <v>129.5192150418257</v>
       </c>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>220</v>
       </c>
@@ -7230,10 +7258,10 @@
         <v>242</v>
       </c>
       <c r="D213">
-        <v>675.4752380952381</v>
+        <v>675.47523809523807</v>
       </c>
       <c r="E213">
-        <v>421.4194761904761</v>
+        <v>421.41947619047608</v>
       </c>
       <c r="F213">
         <v>2.448</v>
@@ -7242,13 +7270,13 @@
         <v>1160</v>
       </c>
       <c r="H213">
-        <v>41712.71914806065</v>
+        <v>41712.719148060649</v>
       </c>
       <c r="I213">
         <v>125.44233902356</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>221</v>
       </c>
@@ -7259,25 +7287,25 @@
         <v>242</v>
       </c>
       <c r="D214">
-        <v>690.1152500000001</v>
+        <v>690.11525000000006</v>
       </c>
       <c r="E214">
-        <v>406.9808</v>
+        <v>406.98079999999999</v>
       </c>
       <c r="F214">
-        <v>2.336</v>
+        <v>2.3359999999999999</v>
       </c>
       <c r="G214">
         <v>1190</v>
       </c>
       <c r="H214">
-        <v>42380.12265442962</v>
+        <v>42380.122654429622</v>
       </c>
       <c r="I214">
-        <v>126.659977801755</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9">
+        <v>126.65997780175501</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>222</v>
       </c>
@@ -7288,25 +7316,25 @@
         <v>242</v>
       </c>
       <c r="D215">
-        <v>729.0744090909092</v>
+        <v>729.07440909090917</v>
       </c>
       <c r="E215">
-        <v>387.572909090909</v>
+        <v>387.57290909090898</v>
       </c>
       <c r="F215">
-        <v>2.451</v>
+        <v>2.4510000000000001</v>
       </c>
       <c r="G215">
         <v>1300</v>
       </c>
       <c r="H215">
-        <v>43185.34498486378</v>
+        <v>43185.344984863783</v>
       </c>
       <c r="I215">
-        <v>135.7880696532945</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9">
+        <v>135.78806965329451</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>223</v>
       </c>
@@ -7317,25 +7345,25 @@
         <v>242</v>
       </c>
       <c r="D216">
-        <v>758.0180952380953</v>
+        <v>758.01809523809527</v>
       </c>
       <c r="E216">
-        <v>370.0074285714286</v>
+        <v>370.00742857142859</v>
       </c>
       <c r="F216">
-        <v>2.118</v>
+        <v>2.1179999999999999</v>
       </c>
       <c r="G216">
         <v>1300</v>
       </c>
       <c r="H216">
-        <v>44005.86653957619</v>
+        <v>44005.866539576193</v>
       </c>
       <c r="I216">
-        <v>133.2562018187386</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9">
+        <v>133.25620181873859</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>224</v>
       </c>
@@ -7349,22 +7377,22 @@
         <v>1091.348</v>
       </c>
       <c r="E217">
-        <v>360.213</v>
+        <v>360.21300000000002</v>
       </c>
       <c r="F217">
-        <v>1.943966</v>
+        <v>1.9439660000000001</v>
       </c>
       <c r="G217">
         <v>1425</v>
       </c>
       <c r="H217">
-        <v>44929.98973690728</v>
+        <v>44929.989736907279</v>
       </c>
       <c r="I217">
-        <v>143.0649345224911</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9">
+        <v>143.06493452249109</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>225</v>
       </c>
@@ -7375,25 +7403,25 @@
         <v>242</v>
       </c>
       <c r="D218">
-        <v>975.0999545454546</v>
+        <v>975.09995454545458</v>
       </c>
       <c r="E218">
-        <v>347.8092727272727</v>
+        <v>347.80927272727268</v>
       </c>
       <c r="F218">
-        <v>2.101128</v>
+        <v>2.1011280000000001</v>
       </c>
       <c r="G218">
         <v>1425</v>
       </c>
       <c r="H218">
-        <v>45963.37950085614</v>
+        <v>45963.379500856143</v>
       </c>
       <c r="I218">
         <v>139.8484208430998</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>226</v>
       </c>
@@ -7404,25 +7432,25 @@
         <v>242</v>
       </c>
       <c r="D219">
-        <v>631.3233333333333</v>
+        <v>631.32333333333327</v>
       </c>
       <c r="E219">
-        <v>323.5692777777778</v>
+        <v>323.56927777777781</v>
       </c>
       <c r="F219">
-        <v>2.468352</v>
+        <v>2.4683519999999999</v>
       </c>
       <c r="G219">
         <v>1415</v>
       </c>
       <c r="H219">
-        <v>47112.46398837754</v>
+        <v>47112.463988377538</v>
       </c>
       <c r="I219">
-        <v>135.4800277230544</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9">
+        <v>135.48002772305441</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>227</v>
       </c>
@@ -7433,25 +7461,25 @@
         <v>242</v>
       </c>
       <c r="D220">
-        <v>598.9416363636363</v>
+        <v>598.94163636363635</v>
       </c>
       <c r="E220">
-        <v>311.7985454545455</v>
+        <v>311.79854545454549</v>
       </c>
       <c r="F220">
-        <v>2.464726</v>
+        <v>2.4647260000000002</v>
       </c>
       <c r="G220">
         <v>1510</v>
       </c>
       <c r="H220">
-        <v>48431.61298005211</v>
+        <v>48431.612980052108</v>
       </c>
       <c r="I220">
-        <v>140.6379960826966</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9">
+        <v>140.63799608269659</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>228</v>
       </c>
@@ -7462,25 +7490,25 @@
         <v>242</v>
       </c>
       <c r="D221">
-        <v>546.7234500000001</v>
+        <v>546.72345000000007</v>
       </c>
       <c r="E221">
-        <v>294.90255</v>
+        <v>294.90255000000002</v>
       </c>
       <c r="F221">
-        <v>2.39687822</v>
+        <v>2.3968782200000001</v>
       </c>
       <c r="G221">
         <v>1450</v>
       </c>
       <c r="H221">
-        <v>49836.12975647362</v>
+        <v>49836.129756473623</v>
       </c>
       <c r="I221">
-        <v>131.2436650512039</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9">
+        <v>131.24366505120389</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>229</v>
       </c>
@@ -7491,25 +7519,25 @@
         <v>242</v>
       </c>
       <c r="D222">
-        <v>519.1478947368421</v>
+        <v>519.14789473684209</v>
       </c>
       <c r="E222">
         <v>287.7625263157895</v>
       </c>
       <c r="F222">
-        <v>2.383406</v>
+        <v>2.3834059999999999</v>
       </c>
       <c r="G222">
         <v>1405</v>
       </c>
       <c r="H222">
-        <v>51281.37751941136</v>
+        <v>51281.377519411362</v>
       </c>
       <c r="I222">
         <v>123.5865751127251</v>
       </c>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>230</v>
       </c>
@@ -7520,25 +7548,25 @@
         <v>242</v>
       </c>
       <c r="D223">
-        <v>585.4601363636364</v>
+        <v>585.46013636363637</v>
       </c>
       <c r="E223">
-        <v>298.5008636363636</v>
+        <v>298.50086363636359</v>
       </c>
       <c r="F223">
-        <v>2.30089</v>
+        <v>2.3008899999999999</v>
       </c>
       <c r="G223">
         <v>1390</v>
       </c>
       <c r="H223">
-        <v>53024.94435507133</v>
+        <v>53024.944355071333</v>
       </c>
       <c r="I223">
         <v>118.2467557883821</v>
       </c>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>231</v>
       </c>
@@ -7549,10 +7577,10 @@
         <v>242</v>
       </c>
       <c r="D224">
-        <v>561.1827272727273</v>
+        <v>561.18272727272733</v>
       </c>
       <c r="E224">
-        <v>276.7695454545455</v>
+        <v>276.76954545454549</v>
       </c>
       <c r="F224">
         <v>2.023031</v>
@@ -7561,13 +7589,13 @@
         <v>1395</v>
       </c>
       <c r="H224">
-        <v>54403.5929083032</v>
+        <v>54403.592908303202</v>
       </c>
       <c r="I224">
-        <v>115.6648185485247</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9">
+        <v>115.66481854852471</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>232</v>
       </c>
@@ -7578,10 +7606,10 @@
         <v>242</v>
       </c>
       <c r="D225">
-        <v>521.26385</v>
+        <v>521.26385000000005</v>
       </c>
       <c r="E225">
-        <v>258.38665</v>
+        <v>258.38664999999997</v>
       </c>
       <c r="F225">
         <v>1.99</v>
@@ -7590,13 +7618,13 @@
         <v>1410</v>
       </c>
       <c r="H225">
-        <v>55546.06835937755</v>
+        <v>55546.068359377547</v>
       </c>
       <c r="I225">
         <v>114.5039434621478</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>233</v>
       </c>
@@ -7607,25 +7635,25 @@
         <v>242</v>
       </c>
       <c r="D226">
-        <v>455.2537619047619</v>
+        <v>455.25376190476192</v>
       </c>
       <c r="E226">
-        <v>251.854</v>
+        <v>251.85400000000001</v>
       </c>
       <c r="F226">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="G226">
         <v>1495</v>
       </c>
       <c r="H226">
-        <v>56601.44365820572</v>
+        <v>56601.443658205717</v>
       </c>
       <c r="I226">
         <v>119.1429474564209</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>234</v>
       </c>
@@ -7636,25 +7664,49 @@
         <v>242</v>
       </c>
       <c r="D227">
-        <v>419.3555</v>
+        <v>419.35550000000001</v>
       </c>
       <c r="E227">
-        <v>252.6550909090909</v>
+        <v>252.65509090909089</v>
       </c>
       <c r="F227">
-        <v>1.93555262226756</v>
+        <v>1.9355526222675601</v>
       </c>
       <c r="G227">
         <v>1540</v>
       </c>
       <c r="H227">
-        <v>57790.07397502804</v>
+        <v>57790.073975028041</v>
       </c>
       <c r="I227">
         <v>120.2048873868744</v>
       </c>
     </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>243</v>
+      </c>
+      <c r="B228" t="s">
+        <v>240</v>
+      </c>
+      <c r="C228" t="s">
+        <v>242</v>
+      </c>
+      <c r="D228">
+        <v>483</v>
+      </c>
+      <c r="E228">
+        <v>253.584</v>
+      </c>
+      <c r="F228">
+        <v>2.06</v>
+      </c>
+      <c r="G228">
+        <v>1590</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/serie_modelo.xlsx
+++ b/data/serie_modelo.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\para cargar simulador electoral arg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F346819FBB6225D5DF1F731669765A205F2BC966" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{144563DA-BB05-4151-B950-4E7B96EF877F}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_F346819FBB6225D5DF1F731669765A205F2BC966" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D285771B-21B7-4684-8F47-4FFE096BA457}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -7704,6 +7717,12 @@
       <c r="G228">
         <v>1590</v>
       </c>
+      <c r="H228">
+        <v>58945.875454528599</v>
+      </c>
+      <c r="I228">
+        <v>121.67416026555289</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
